--- a/prix/pex.xlsx
+++ b/prix/pex.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\caisse5\Desktop\site-internet\raccords-plomberie\prix\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\raccords-plomberie\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0B84138-F4B2-4EC4-9F03-6256DED36F6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8398F9B4-34CF-4FF1-BDEF-8E8C1625FDC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{C27940F6-7049-4028-8D53-A9BC0C24D70B}"/>
   </bookViews>
@@ -991,7 +991,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="#,##0.000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -1087,7 +1087,7 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1645,7 +1645,7 @@
         <v>15</v>
       </c>
       <c r="F10" s="12">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
@@ -1762,7 +1762,7 @@
         <v>26</v>
       </c>
       <c r="F16" s="12">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.3">
@@ -1779,7 +1779,7 @@
         <v>28</v>
       </c>
       <c r="F17" s="12">
-        <v>2.8</v>
+        <v>4.8000000000000025</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.3">
@@ -1790,7 +1790,7 @@
         <v>267</v>
       </c>
       <c r="D18" s="13">
-        <v>141.72</v>
+        <v>106.87</v>
       </c>
       <c r="E18" s="8" t="s">
         <v>30</v>
@@ -1807,13 +1807,13 @@
         <v>267</v>
       </c>
       <c r="D19" s="13">
-        <v>141.72</v>
+        <v>111.32000000000001</v>
       </c>
       <c r="E19" s="8" t="s">
         <v>32</v>
       </c>
       <c r="F19" s="12">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.3">
@@ -1864,7 +1864,7 @@
         <v>38</v>
       </c>
       <c r="F22" s="12">
-        <v>449</v>
+        <v>445</v>
       </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.3">
@@ -1881,7 +1881,7 @@
         <v>40</v>
       </c>
       <c r="F23" s="12">
-        <v>315</v>
+        <v>295</v>
       </c>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.3">
@@ -1898,7 +1898,7 @@
         <v>42</v>
       </c>
       <c r="F24" s="12">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.3">
@@ -2007,7 +2007,7 @@
         <v>267</v>
       </c>
       <c r="D31" s="13">
-        <v>70.37</v>
+        <v>66.790000000000006</v>
       </c>
       <c r="E31" s="8" t="s">
         <v>56</v>
@@ -2099,7 +2099,7 @@
         <v>43123030</v>
       </c>
       <c r="F36" s="12">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
@@ -2159,7 +2159,7 @@
         <v>70</v>
       </c>
       <c r="F39" s="12">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
@@ -2239,7 +2239,7 @@
         <v>78</v>
       </c>
       <c r="F43" s="12">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
@@ -2293,13 +2293,13 @@
         <v>270</v>
       </c>
       <c r="D46" s="13">
-        <v>8.68</v>
+        <v>8.69</v>
       </c>
       <c r="E46" s="8" t="s">
         <v>84</v>
       </c>
       <c r="F46" s="12">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
@@ -2543,7 +2543,7 @@
         <v>110</v>
       </c>
       <c r="F59" s="12">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
@@ -2581,7 +2581,7 @@
         <v>114</v>
       </c>
       <c r="F61" s="12">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
@@ -2601,7 +2601,7 @@
         <v>116</v>
       </c>
       <c r="F62" s="12">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
@@ -2752,7 +2752,7 @@
         <v>132</v>
       </c>
       <c r="F70" s="12">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
@@ -2783,13 +2783,13 @@
         <v>274</v>
       </c>
       <c r="D72" s="13">
-        <v>0.68</v>
+        <v>1.6500000000000001</v>
       </c>
       <c r="E72" s="8" t="s">
         <v>136</v>
       </c>
       <c r="F72" s="12">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
@@ -2800,13 +2800,13 @@
         <v>274</v>
       </c>
       <c r="D73" s="13">
-        <v>0.68</v>
+        <v>1.6500000000000001</v>
       </c>
       <c r="E73" s="8" t="s">
         <v>138</v>
       </c>
       <c r="F73" s="12">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
@@ -2826,7 +2826,7 @@
         <v>140</v>
       </c>
       <c r="F74" s="12">
-        <v>77</v>
+        <v>62</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
@@ -2946,7 +2946,7 @@
         <v>152</v>
       </c>
       <c r="F80" s="12">
-        <v>74</v>
+        <v>62</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
@@ -3166,7 +3166,7 @@
         <v>174</v>
       </c>
       <c r="F91" s="12">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
@@ -3206,7 +3206,7 @@
         <v>178</v>
       </c>
       <c r="F93" s="12">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
@@ -3226,7 +3226,7 @@
         <v>180</v>
       </c>
       <c r="F94" s="12">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
@@ -3286,7 +3286,7 @@
         <v>186</v>
       </c>
       <c r="F97" s="12">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
@@ -3346,7 +3346,7 @@
         <v>192</v>
       </c>
       <c r="F100" s="12">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
@@ -3692,7 +3692,7 @@
         <v>227</v>
       </c>
       <c r="F118" s="12">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
@@ -3909,7 +3909,7 @@
         <v>43107594</v>
       </c>
       <c r="F129" s="11">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/prix/pex.xlsx
+++ b/prix/pex.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\raccords-plomberie\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8398F9B4-34CF-4FF1-BDEF-8E8C1625FDC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8743696D-4E8A-44E5-8055-EE199887F120}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{C27940F6-7049-4028-8D53-A9BC0C24D70B}"/>
   </bookViews>
@@ -1087,10 +1087,10 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -1478,14 +1478,14 @@
       <c r="C2" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="D2" s="13">
+      <c r="D2" s="12">
         <v>5.49</v>
       </c>
       <c r="E2" s="8">
         <v>43122970</v>
       </c>
-      <c r="F2" s="12">
-        <v>14</v>
+      <c r="F2" s="13">
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -1498,14 +1498,14 @@
       <c r="C3" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="D3" s="13">
+      <c r="D3" s="12">
         <v>8.8000000000000007</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="12">
-        <v>33</v>
+      <c r="F3" s="13">
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
@@ -1518,13 +1518,13 @@
       <c r="C4" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="12">
         <v>11.68</v>
       </c>
       <c r="E4" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="12">
+      <c r="F4" s="13">
         <v>10</v>
       </c>
     </row>
@@ -1538,14 +1538,14 @@
       <c r="C5" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="D5" s="13">
+      <c r="D5" s="12">
         <v>5.23</v>
       </c>
       <c r="E5" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="12">
-        <v>34</v>
+      <c r="F5" s="13">
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
@@ -1558,14 +1558,14 @@
       <c r="C6" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="12">
         <v>8.2799999999999994</v>
       </c>
       <c r="E6" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="F6" s="12">
-        <v>13</v>
+      <c r="F6" s="13">
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
@@ -1578,13 +1578,13 @@
       <c r="C7" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="D7" s="13">
+      <c r="D7" s="12">
         <v>10.97</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="12">
+      <c r="F7" s="13">
         <v>5</v>
       </c>
     </row>
@@ -1598,14 +1598,14 @@
       <c r="C8" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="D8" s="13">
+      <c r="D8" s="12">
         <v>4.9000000000000004</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="12">
-        <v>226</v>
+      <c r="F8" s="13">
+        <v>224</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
@@ -1618,13 +1618,13 @@
       <c r="C9" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="12">
         <v>5.28</v>
       </c>
       <c r="E9" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F9" s="12">
+      <c r="F9" s="13">
         <v>86</v>
       </c>
     </row>
@@ -1638,13 +1638,13 @@
       <c r="C10" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="D10" s="13">
+      <c r="D10" s="12">
         <v>8.6</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="13">
         <v>90</v>
       </c>
     </row>
@@ -1658,14 +1658,14 @@
       <c r="C11" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="D11" s="13">
+      <c r="D11" s="12">
         <v>2.2000000000000002</v>
       </c>
       <c r="E11" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="F11" s="12">
-        <v>59</v>
+      <c r="F11" s="13">
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
@@ -1678,13 +1678,13 @@
       <c r="C12" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="D12" s="13">
+      <c r="D12" s="12">
         <v>7.19</v>
       </c>
       <c r="E12" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F12" s="12">
+      <c r="F12" s="13">
         <v>43</v>
       </c>
     </row>
@@ -1698,13 +1698,13 @@
       <c r="C13" s="6" t="s">
         <v>257</v>
       </c>
-      <c r="D13" s="13">
+      <c r="D13" s="12">
         <v>5.94</v>
       </c>
       <c r="E13" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="F13" s="12">
+      <c r="F13" s="13">
         <v>58</v>
       </c>
     </row>
@@ -1718,13 +1718,13 @@
       <c r="C14" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="D14" s="13">
+      <c r="D14" s="12">
         <v>8.1999999999999993</v>
       </c>
       <c r="E14" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="F14" s="12">
+      <c r="F14" s="13">
         <v>54</v>
       </c>
     </row>
@@ -1738,13 +1738,13 @@
       <c r="C15" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="D15" s="13">
+      <c r="D15" s="12">
         <v>9.4500000000000011</v>
       </c>
       <c r="E15" s="8">
         <v>43122988</v>
       </c>
-      <c r="F15" s="12">
+      <c r="F15" s="13">
         <v>12</v>
       </c>
     </row>
@@ -1755,14 +1755,14 @@
       <c r="C16" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="D16" s="13">
-        <v>96.15</v>
+      <c r="D16" s="12">
+        <v>76.790000000000006</v>
       </c>
       <c r="E16" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="F16" s="12">
-        <v>3</v>
+      <c r="F16" s="13">
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.3">
@@ -1772,14 +1772,14 @@
       <c r="C17" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="D17" s="13">
-        <v>88.9</v>
+      <c r="D17" s="12">
+        <v>76.790000000000006</v>
       </c>
       <c r="E17" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="F17" s="12">
-        <v>4.8000000000000025</v>
+      <c r="F17" s="13">
+        <v>14.800000000000002</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.3">
@@ -1789,14 +1789,14 @@
       <c r="C18" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="D18" s="13">
+      <c r="D18" s="12">
         <v>106.87</v>
       </c>
       <c r="E18" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F18" s="12">
-        <v>3</v>
+      <c r="F18" s="13">
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.3">
@@ -1806,13 +1806,13 @@
       <c r="C19" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="D19" s="13">
-        <v>111.32000000000001</v>
+      <c r="D19" s="12">
+        <v>106.87</v>
       </c>
       <c r="E19" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F19" s="12">
+      <c r="F19" s="13">
         <v>4</v>
       </c>
     </row>
@@ -1823,14 +1823,14 @@
       <c r="C20" s="6" t="s">
         <v>281</v>
       </c>
-      <c r="D20" s="13">
-        <v>63.08</v>
+      <c r="D20" s="12">
+        <v>76.790000000000006</v>
       </c>
       <c r="E20" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="F20" s="12">
-        <v>0</v>
+      <c r="F20" s="13">
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.3">
@@ -1840,14 +1840,14 @@
       <c r="C21" s="6" t="s">
         <v>281</v>
       </c>
-      <c r="D21" s="13">
-        <v>63.08</v>
+      <c r="D21" s="12">
+        <v>76.790000000000006</v>
       </c>
       <c r="E21" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="F21" s="12">
-        <v>0</v>
+      <c r="F21" s="13">
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.3">
@@ -1857,14 +1857,14 @@
       <c r="C22" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="D22" s="13">
+      <c r="D22" s="12">
         <v>2.0100000000000002</v>
       </c>
       <c r="E22" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="F22" s="12">
-        <v>445</v>
+      <c r="F22" s="13">
+        <v>354</v>
       </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.3">
@@ -1874,14 +1874,14 @@
       <c r="C23" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="D23" s="13">
+      <c r="D23" s="12">
         <v>3.75</v>
       </c>
       <c r="E23" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F23" s="12">
-        <v>295</v>
+      <c r="F23" s="13">
+        <v>224</v>
       </c>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.3">
@@ -1891,14 +1891,14 @@
       <c r="C24" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="D24" s="13">
+      <c r="D24" s="12">
         <v>7.07</v>
       </c>
       <c r="E24" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="F24" s="12">
-        <v>84</v>
+      <c r="F24" s="13">
+        <v>72</v>
       </c>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.3">
@@ -1906,13 +1906,13 @@
         <v>45</v>
       </c>
       <c r="C25" s="6"/>
-      <c r="D25" s="13">
-        <v>12.61</v>
+      <c r="D25" s="12">
+        <v>12.200000000000001</v>
       </c>
       <c r="E25" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="F25" s="12">
+      <c r="F25" s="13">
         <v>0</v>
       </c>
     </row>
@@ -1923,13 +1923,13 @@
       <c r="C26" s="6" t="s">
         <v>272</v>
       </c>
-      <c r="D26" s="13">
-        <v>8.65</v>
+      <c r="D26" s="12">
+        <v>8.35</v>
       </c>
       <c r="E26" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="F26" s="12">
+      <c r="F26" s="13">
         <v>0</v>
       </c>
     </row>
@@ -1938,13 +1938,13 @@
         <v>49</v>
       </c>
       <c r="C27" s="6"/>
-      <c r="D27" s="13">
+      <c r="D27" s="12">
         <v>208.51</v>
       </c>
       <c r="E27" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="F27" s="12">
+      <c r="F27" s="13">
         <v>1</v>
       </c>
     </row>
@@ -1955,13 +1955,13 @@
       <c r="C28" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="D28" s="13">
+      <c r="D28" s="12">
         <v>157.20000000000002</v>
       </c>
       <c r="E28" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="F28" s="12">
+      <c r="F28" s="13">
         <v>3</v>
       </c>
     </row>
@@ -1972,14 +1972,14 @@
       <c r="C29" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="D29" s="13">
-        <v>67.8</v>
+      <c r="D29" s="12">
+        <v>53.43</v>
       </c>
       <c r="E29" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="F29" s="12">
-        <v>1.9999999999999876</v>
+      <c r="F29" s="13">
+        <v>-1.0000000000000124</v>
       </c>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.3">
@@ -1989,13 +1989,13 @@
       <c r="C30" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="D30" s="13">
+      <c r="D30" s="12">
         <v>106.87</v>
       </c>
       <c r="E30" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="F30" s="12">
+      <c r="F30" s="13">
         <v>3.0000000000000133</v>
       </c>
     </row>
@@ -2006,13 +2006,13 @@
       <c r="C31" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="D31" s="13">
-        <v>66.790000000000006</v>
+      <c r="D31" s="12">
+        <v>53.43</v>
       </c>
       <c r="E31" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="F31" s="12">
+      <c r="F31" s="13">
         <v>-1.2434497875801753E-14</v>
       </c>
     </row>
@@ -2023,14 +2023,14 @@
       <c r="C32" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="D32" s="13">
+      <c r="D32" s="12">
         <v>106.87</v>
       </c>
       <c r="E32" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="F32" s="12">
-        <v>5.0000000000000213</v>
+      <c r="F32" s="13">
+        <v>2.600000000000021</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
@@ -2040,14 +2040,14 @@
       <c r="C33" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="D33" s="13">
+      <c r="D33" s="12">
         <v>158.75</v>
       </c>
       <c r="E33" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="F33" s="12">
-        <v>250</v>
+      <c r="F33" s="13">
+        <v>249</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
@@ -2057,13 +2057,13 @@
       <c r="C34" s="6" t="s">
         <v>273</v>
       </c>
-      <c r="D34" s="13">
+      <c r="D34" s="12">
         <v>3.17</v>
       </c>
       <c r="E34" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="F34" s="12">
+      <c r="F34" s="13">
         <v>0</v>
       </c>
     </row>
@@ -2072,13 +2072,13 @@
         <v>64</v>
       </c>
       <c r="C35" s="6"/>
-      <c r="D35" s="13">
+      <c r="D35" s="12">
         <v>45.910000000000004</v>
       </c>
       <c r="E35" s="8">
         <v>43123024</v>
       </c>
-      <c r="F35" s="12">
+      <c r="F35" s="13">
         <v>0</v>
       </c>
     </row>
@@ -2092,14 +2092,14 @@
       <c r="C36" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="D36" s="13">
+      <c r="D36" s="12">
         <v>3.61</v>
       </c>
       <c r="E36" s="8">
         <v>43123030</v>
       </c>
-      <c r="F36" s="12">
-        <v>147</v>
+      <c r="F36" s="13">
+        <v>135</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
@@ -2112,13 +2112,13 @@
       <c r="C37" s="6" t="s">
         <v>257</v>
       </c>
-      <c r="D37" s="13">
+      <c r="D37" s="12">
         <v>5.8</v>
       </c>
       <c r="E37" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="F37" s="12">
+      <c r="F37" s="13">
         <v>17</v>
       </c>
     </row>
@@ -2132,14 +2132,14 @@
       <c r="C38" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="D38" s="13">
+      <c r="D38" s="12">
         <v>5.93</v>
       </c>
       <c r="E38" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="F38" s="12">
-        <v>46</v>
+      <c r="F38" s="13">
+        <v>44</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
@@ -2152,14 +2152,14 @@
       <c r="C39" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="D39" s="13">
+      <c r="D39" s="12">
         <v>5.71</v>
       </c>
       <c r="E39" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="F39" s="12">
-        <v>5</v>
+      <c r="F39" s="13">
+        <v>23</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
@@ -2172,14 +2172,14 @@
       <c r="C40" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="D40" s="13">
+      <c r="D40" s="12">
         <v>9.7200000000000006</v>
       </c>
       <c r="E40" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="F40" s="12">
-        <v>5</v>
+      <c r="F40" s="13">
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
@@ -2192,14 +2192,14 @@
       <c r="C41" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="D41" s="13">
+      <c r="D41" s="12">
         <v>4.6900000000000004</v>
       </c>
       <c r="E41" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="F41" s="12">
-        <v>64</v>
+      <c r="F41" s="13">
+        <v>52</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
@@ -2212,13 +2212,13 @@
       <c r="C42" s="6" t="s">
         <v>257</v>
       </c>
-      <c r="D42" s="13">
+      <c r="D42" s="12">
         <v>5.49</v>
       </c>
       <c r="E42" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="F42" s="12">
+      <c r="F42" s="13">
         <v>0</v>
       </c>
     </row>
@@ -2232,14 +2232,14 @@
       <c r="C43" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="D43" s="13">
+      <c r="D43" s="12">
         <v>6.0600000000000005</v>
       </c>
       <c r="E43" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="F43" s="12">
-        <v>12</v>
+      <c r="F43" s="13">
+        <v>9</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
@@ -2252,14 +2252,14 @@
       <c r="C44" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="D44" s="13">
+      <c r="D44" s="12">
         <v>6.22</v>
       </c>
       <c r="E44" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="F44" s="12">
-        <v>40</v>
+      <c r="F44" s="13">
+        <v>38</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
@@ -2272,14 +2272,14 @@
       <c r="C45" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="D45" s="13">
+      <c r="D45" s="12">
         <v>9.64</v>
       </c>
       <c r="E45" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="F45" s="12">
-        <v>6</v>
+      <c r="F45" s="13">
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
@@ -2292,14 +2292,14 @@
       <c r="C46" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="D46" s="13">
+      <c r="D46" s="12">
         <v>8.69</v>
       </c>
       <c r="E46" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="F46" s="12">
-        <v>2</v>
+      <c r="F46" s="13">
+        <v>20</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
@@ -2310,13 +2310,13 @@
         <v>87</v>
       </c>
       <c r="C47" s="6"/>
-      <c r="D47" s="13">
+      <c r="D47" s="12">
         <v>11.8</v>
       </c>
       <c r="E47" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="F47" s="12">
+      <c r="F47" s="13">
         <v>35</v>
       </c>
     </row>
@@ -2330,13 +2330,13 @@
       <c r="C48" s="6" t="s">
         <v>271</v>
       </c>
-      <c r="D48" s="13">
+      <c r="D48" s="12">
         <v>18.05</v>
       </c>
       <c r="E48" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="F48" s="12">
+      <c r="F48" s="13">
         <v>33</v>
       </c>
     </row>
@@ -2350,13 +2350,13 @@
       <c r="C49" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="D49" s="13">
+      <c r="D49" s="12">
         <v>8.370000000000001</v>
       </c>
       <c r="E49" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="F49" s="12">
+      <c r="F49" s="13">
         <v>21</v>
       </c>
     </row>
@@ -2370,14 +2370,14 @@
       <c r="C50" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="D50" s="13">
+      <c r="D50" s="12">
         <v>15.88</v>
       </c>
       <c r="E50" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="F50" s="12">
-        <v>43</v>
+      <c r="F50" s="13">
+        <v>41</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
@@ -2385,13 +2385,13 @@
         <v>95</v>
       </c>
       <c r="C51" s="6"/>
-      <c r="D51" s="13">
+      <c r="D51" s="12">
         <v>9.75</v>
       </c>
       <c r="E51" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="F51" s="12">
+      <c r="F51" s="13">
         <v>0</v>
       </c>
     </row>
@@ -2400,13 +2400,13 @@
         <v>97</v>
       </c>
       <c r="C52" s="6"/>
-      <c r="D52" s="13">
+      <c r="D52" s="12">
         <v>11.08</v>
       </c>
       <c r="E52" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="F52" s="12">
+      <c r="F52" s="13">
         <v>0</v>
       </c>
     </row>
@@ -2420,13 +2420,13 @@
       <c r="C53" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="D53" s="13">
+      <c r="D53" s="12">
         <v>17.21</v>
       </c>
       <c r="E53" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="F53" s="12">
+      <c r="F53" s="13">
         <v>9</v>
       </c>
     </row>
@@ -2440,13 +2440,13 @@
       <c r="C54" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="D54" s="13">
+      <c r="D54" s="12">
         <v>13.66</v>
       </c>
       <c r="E54" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="F54" s="12">
+      <c r="F54" s="13">
         <v>22</v>
       </c>
     </row>
@@ -2460,13 +2460,13 @@
       <c r="C55" s="6" t="s">
         <v>261</v>
       </c>
-      <c r="D55" s="13">
+      <c r="D55" s="12">
         <v>13.88</v>
       </c>
       <c r="E55" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="F55" s="12">
+      <c r="F55" s="13">
         <v>18</v>
       </c>
     </row>
@@ -2480,13 +2480,13 @@
       <c r="C56" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="D56" s="13">
+      <c r="D56" s="12">
         <v>21.26</v>
       </c>
       <c r="E56" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="F56" s="12">
+      <c r="F56" s="13">
         <v>0</v>
       </c>
     </row>
@@ -2500,13 +2500,13 @@
       <c r="C57" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="D57" s="13">
+      <c r="D57" s="12">
         <v>21.26</v>
       </c>
       <c r="E57" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="F57" s="12">
+      <c r="F57" s="13">
         <v>0</v>
       </c>
     </row>
@@ -2518,14 +2518,14 @@
         <v>109</v>
       </c>
       <c r="C58" s="6"/>
-      <c r="D58" s="13">
+      <c r="D58" s="12">
         <v>6.15</v>
       </c>
       <c r="E58" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="F58" s="12">
-        <v>36</v>
+      <c r="F58" s="13">
+        <v>18</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
@@ -2536,13 +2536,13 @@
         <v>111</v>
       </c>
       <c r="C59" s="6"/>
-      <c r="D59" s="13">
+      <c r="D59" s="12">
         <v>9.99</v>
       </c>
       <c r="E59" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="F59" s="12">
+      <c r="F59" s="13">
         <v>13</v>
       </c>
     </row>
@@ -2554,13 +2554,13 @@
         <v>113</v>
       </c>
       <c r="C60" s="6"/>
-      <c r="D60" s="13">
+      <c r="D60" s="12">
         <v>15.49</v>
       </c>
       <c r="E60" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="F60" s="12">
+      <c r="F60" s="13">
         <v>8</v>
       </c>
     </row>
@@ -2574,13 +2574,13 @@
       <c r="C61" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="D61" s="13">
+      <c r="D61" s="12">
         <v>20.34</v>
       </c>
       <c r="E61" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="F61" s="12">
+      <c r="F61" s="13">
         <v>2</v>
       </c>
     </row>
@@ -2594,14 +2594,14 @@
       <c r="C62" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="D62" s="13">
+      <c r="D62" s="12">
         <v>6.92</v>
       </c>
       <c r="E62" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="F62" s="12">
-        <v>10</v>
+      <c r="F62" s="13">
+        <v>6</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
@@ -2614,13 +2614,13 @@
       <c r="C63" s="6" t="s">
         <v>257</v>
       </c>
-      <c r="D63" s="13">
+      <c r="D63" s="12">
         <v>8.39</v>
       </c>
       <c r="E63" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="F63" s="12">
+      <c r="F63" s="13">
         <v>11</v>
       </c>
     </row>
@@ -2631,13 +2631,13 @@
       <c r="C64" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="D64" s="13">
+      <c r="D64" s="12">
         <v>4.4000000000000004</v>
       </c>
       <c r="E64" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="F64" s="12">
+      <c r="F64" s="13">
         <v>0</v>
       </c>
     </row>
@@ -2648,13 +2648,13 @@
       <c r="C65" s="6" t="s">
         <v>275</v>
       </c>
-      <c r="D65" s="13">
+      <c r="D65" s="12">
         <v>9.99</v>
       </c>
       <c r="E65" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="F65" s="12">
+      <c r="F65" s="13">
         <v>2</v>
       </c>
     </row>
@@ -2665,13 +2665,13 @@
       <c r="C66" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="D66" s="13">
+      <c r="D66" s="12">
         <v>9.99</v>
       </c>
       <c r="E66" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="F66" s="12">
+      <c r="F66" s="13">
         <v>4</v>
       </c>
     </row>
@@ -2685,14 +2685,14 @@
       <c r="C67" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="D67" s="13">
+      <c r="D67" s="12">
         <v>5.53</v>
       </c>
       <c r="E67" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="F67" s="12">
-        <v>37</v>
+      <c r="F67" s="13">
+        <v>27</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
@@ -2705,14 +2705,14 @@
       <c r="C68" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="D68" s="13">
+      <c r="D68" s="12">
         <v>8.8000000000000007</v>
       </c>
       <c r="E68" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="F68" s="12">
-        <v>21</v>
+      <c r="F68" s="13">
+        <v>19</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
@@ -2725,13 +2725,13 @@
       <c r="C69" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="D69" s="13">
+      <c r="D69" s="12">
         <v>13.77</v>
       </c>
       <c r="E69" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="F69" s="12">
+      <c r="F69" s="13">
         <v>12</v>
       </c>
     </row>
@@ -2745,14 +2745,14 @@
       <c r="C70" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="D70" s="13">
+      <c r="D70" s="12">
         <v>4.71</v>
       </c>
       <c r="E70" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="F70" s="12">
-        <v>19</v>
+      <c r="F70" s="13">
+        <v>17</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
@@ -2765,13 +2765,13 @@
       <c r="C71" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="D71" s="13">
+      <c r="D71" s="12">
         <v>5.42</v>
       </c>
       <c r="E71" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="F71" s="12">
+      <c r="F71" s="13">
         <v>9</v>
       </c>
     </row>
@@ -2782,14 +2782,14 @@
       <c r="C72" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D72" s="13">
+      <c r="D72" s="12">
         <v>1.6500000000000001</v>
       </c>
       <c r="E72" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="F72" s="12">
-        <v>5</v>
+      <c r="F72" s="13">
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
@@ -2799,14 +2799,14 @@
       <c r="C73" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D73" s="13">
+      <c r="D73" s="12">
         <v>1.6500000000000001</v>
       </c>
       <c r="E73" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="F73" s="12">
-        <v>5</v>
+      <c r="F73" s="13">
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
@@ -2819,14 +2819,14 @@
       <c r="C74" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="D74" s="13">
+      <c r="D74" s="12">
         <v>7.96</v>
       </c>
       <c r="E74" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="F74" s="12">
-        <v>62</v>
+      <c r="F74" s="13">
+        <v>101</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
@@ -2839,14 +2839,14 @@
       <c r="C75" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="D75" s="13">
+      <c r="D75" s="12">
         <v>19.14</v>
       </c>
       <c r="E75" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="F75" s="12">
-        <v>14</v>
+      <c r="F75" s="13">
+        <v>9</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
@@ -2859,14 +2859,14 @@
       <c r="C76" s="6" t="s">
         <v>279</v>
       </c>
-      <c r="D76" s="13">
+      <c r="D76" s="12">
         <v>23.35</v>
       </c>
       <c r="E76" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="F76" s="12">
-        <v>17</v>
+      <c r="F76" s="13">
+        <v>16</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
@@ -2879,14 +2879,14 @@
       <c r="C77" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="D77" s="13">
+      <c r="D77" s="12">
         <v>9.9700000000000006</v>
       </c>
       <c r="E77" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="F77" s="12">
-        <v>10</v>
+      <c r="F77" s="13">
+        <v>20</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
@@ -2899,13 +2899,13 @@
       <c r="C78" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="D78" s="13">
+      <c r="D78" s="12">
         <v>10.620000000000001</v>
       </c>
       <c r="E78" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="F78" s="12">
+      <c r="F78" s="13">
         <v>13</v>
       </c>
     </row>
@@ -2919,13 +2919,13 @@
       <c r="C79" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="D79" s="13">
+      <c r="D79" s="12">
         <v>11.86</v>
       </c>
       <c r="E79" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="F79" s="12">
+      <c r="F79" s="13">
         <v>0</v>
       </c>
     </row>
@@ -2939,14 +2939,14 @@
       <c r="C80" s="6" t="s">
         <v>265</v>
       </c>
-      <c r="D80" s="13">
+      <c r="D80" s="12">
         <v>10.55</v>
       </c>
       <c r="E80" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="F80" s="12">
-        <v>62</v>
+      <c r="F80" s="13">
+        <v>56</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
@@ -2959,14 +2959,14 @@
       <c r="C81" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="D81" s="13">
+      <c r="D81" s="12">
         <v>12.63</v>
       </c>
       <c r="E81" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="F81" s="12">
-        <v>45</v>
+      <c r="F81" s="13">
+        <v>42</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
@@ -2979,13 +2979,13 @@
       <c r="C82" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="D82" s="13">
+      <c r="D82" s="12">
         <v>13.89</v>
       </c>
       <c r="E82" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="F82" s="12">
+      <c r="F82" s="13">
         <v>9</v>
       </c>
     </row>
@@ -2999,14 +2999,14 @@
       <c r="C83" s="6" t="s">
         <v>261</v>
       </c>
-      <c r="D83" s="13">
+      <c r="D83" s="12">
         <v>12.1</v>
       </c>
       <c r="E83" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="F83" s="12">
-        <v>14</v>
+      <c r="F83" s="13">
+        <v>33</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
@@ -3019,13 +3019,13 @@
       <c r="C84" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="D84" s="13">
+      <c r="D84" s="12">
         <v>13.31</v>
       </c>
       <c r="E84" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="F84" s="12">
+      <c r="F84" s="13">
         <v>33</v>
       </c>
     </row>
@@ -3039,13 +3039,13 @@
       <c r="C85" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="D85" s="13">
+      <c r="D85" s="12">
         <v>23.62</v>
       </c>
       <c r="E85" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="F85" s="12">
+      <c r="F85" s="13">
         <v>24</v>
       </c>
     </row>
@@ -3059,14 +3059,14 @@
       <c r="C86" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="D86" s="13">
+      <c r="D86" s="12">
         <v>6.61</v>
       </c>
       <c r="E86" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="F86" s="12">
-        <v>27</v>
+      <c r="F86" s="13">
+        <v>3</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
@@ -3079,13 +3079,13 @@
       <c r="C87" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="D87" s="13">
+      <c r="D87" s="12">
         <v>7.55</v>
       </c>
       <c r="E87" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="F87" s="12">
+      <c r="F87" s="13">
         <v>30</v>
       </c>
     </row>
@@ -3099,13 +3099,13 @@
       <c r="C88" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="D88" s="13">
+      <c r="D88" s="12">
         <v>8.86</v>
       </c>
       <c r="E88" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="F88" s="12">
+      <c r="F88" s="13">
         <v>38</v>
       </c>
     </row>
@@ -3119,13 +3119,13 @@
       <c r="C89" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="D89" s="13">
+      <c r="D89" s="12">
         <v>1.82</v>
       </c>
       <c r="E89" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="F89" s="12">
+      <c r="F89" s="13">
         <v>92</v>
       </c>
     </row>
@@ -3139,13 +3139,13 @@
       <c r="C90" s="6" t="s">
         <v>257</v>
       </c>
-      <c r="D90" s="13">
+      <c r="D90" s="12">
         <v>4.8899999999999997</v>
       </c>
       <c r="E90" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="F90" s="12">
+      <c r="F90" s="13">
         <v>76</v>
       </c>
     </row>
@@ -3159,14 +3159,14 @@
       <c r="C91" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="D91" s="13">
+      <c r="D91" s="12">
         <v>5.42</v>
       </c>
       <c r="E91" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="F91" s="12">
-        <v>57</v>
+      <c r="F91" s="13">
+        <v>56</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
@@ -3179,14 +3179,14 @@
       <c r="C92" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="D92" s="13">
+      <c r="D92" s="12">
         <v>5.1100000000000003</v>
       </c>
       <c r="E92" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="F92" s="12">
-        <v>52</v>
+      <c r="F92" s="13">
+        <v>51</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
@@ -3199,14 +3199,14 @@
       <c r="C93" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="D93" s="13">
+      <c r="D93" s="12">
         <v>10.02</v>
       </c>
       <c r="E93" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="F93" s="12">
-        <v>0</v>
+      <c r="F93" s="13">
+        <v>10</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
@@ -3219,14 +3219,14 @@
       <c r="C94" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="D94" s="13">
+      <c r="D94" s="12">
         <v>2.1800000000000002</v>
       </c>
       <c r="E94" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="F94" s="12">
-        <v>48</v>
+      <c r="F94" s="13">
+        <v>23</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
@@ -3239,13 +3239,13 @@
       <c r="C95" s="6" t="s">
         <v>257</v>
       </c>
-      <c r="D95" s="13">
+      <c r="D95" s="12">
         <v>8.32</v>
       </c>
       <c r="E95" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="F95" s="12">
+      <c r="F95" s="13">
         <v>88</v>
       </c>
     </row>
@@ -3259,13 +3259,13 @@
       <c r="C96" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="D96" s="13">
+      <c r="D96" s="12">
         <v>8.32</v>
       </c>
       <c r="E96" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="F96" s="12">
+      <c r="F96" s="13">
         <v>84</v>
       </c>
     </row>
@@ -3279,14 +3279,14 @@
       <c r="C97" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="D97" s="13">
+      <c r="D97" s="12">
         <v>7.84</v>
       </c>
       <c r="E97" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="F97" s="12">
-        <v>20</v>
+      <c r="F97" s="13">
+        <v>49</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
@@ -3299,13 +3299,13 @@
       <c r="C98" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="D98" s="13">
+      <c r="D98" s="12">
         <v>13.31</v>
       </c>
       <c r="E98" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="F98" s="12">
+      <c r="F98" s="13">
         <v>0</v>
       </c>
     </row>
@@ -3319,14 +3319,14 @@
       <c r="C99" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="D99" s="13">
+      <c r="D99" s="12">
         <v>8.25</v>
       </c>
       <c r="E99" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="F99" s="12">
-        <v>88</v>
+      <c r="F99" s="13">
+        <v>86</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
@@ -3339,13 +3339,13 @@
       <c r="C100" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="D100" s="13">
+      <c r="D100" s="12">
         <v>6.87</v>
       </c>
       <c r="E100" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="F100" s="12">
+      <c r="F100" s="13">
         <v>35</v>
       </c>
     </row>
@@ -3359,13 +3359,13 @@
       <c r="C101" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="D101" s="13">
+      <c r="D101" s="12">
         <v>26.18</v>
       </c>
       <c r="E101" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="F101" s="12">
+      <c r="F101" s="13">
         <v>0</v>
       </c>
     </row>
@@ -3379,14 +3379,14 @@
       <c r="C102" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="D102" s="13">
-        <v>5.95</v>
+      <c r="D102" s="12">
+        <v>8.4700000000000006</v>
       </c>
       <c r="E102" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="F102" s="12">
-        <v>1</v>
+      <c r="F102" s="13">
+        <v>106</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
@@ -3399,14 +3399,14 @@
       <c r="C103" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="D103" s="13">
+      <c r="D103" s="12">
         <v>9.6300000000000008</v>
       </c>
       <c r="E103" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="F103" s="12">
-        <v>52</v>
+      <c r="F103" s="13">
+        <v>48</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
@@ -3419,14 +3419,14 @@
       <c r="C104" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="D104" s="13">
+      <c r="D104" s="12">
         <v>10.48</v>
       </c>
       <c r="E104" s="8" t="s">
         <v>200</v>
       </c>
-      <c r="F104" s="12">
-        <v>9</v>
+      <c r="F104" s="13">
+        <v>29</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
@@ -3439,13 +3439,13 @@
       <c r="C105" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="D105" s="13">
+      <c r="D105" s="12">
         <v>6.61</v>
       </c>
       <c r="E105" s="8" t="s">
         <v>202</v>
       </c>
-      <c r="F105" s="12">
+      <c r="F105" s="13">
         <v>53</v>
       </c>
     </row>
@@ -3459,14 +3459,14 @@
       <c r="C106" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="D106" s="13">
+      <c r="D106" s="12">
         <v>5.83</v>
       </c>
       <c r="E106" s="8" t="s">
         <v>204</v>
       </c>
-      <c r="F106" s="12">
-        <v>26</v>
+      <c r="F106" s="13">
+        <v>21</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
@@ -3479,13 +3479,13 @@
       <c r="C107" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="D107" s="13">
+      <c r="D107" s="12">
         <v>5.83</v>
       </c>
       <c r="E107" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="F107" s="12">
+      <c r="F107" s="13">
         <v>3</v>
       </c>
     </row>
@@ -3499,13 +3499,13 @@
       <c r="C108" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="D108" s="13">
+      <c r="D108" s="12">
         <v>13.02</v>
       </c>
       <c r="E108" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="F108" s="12">
+      <c r="F108" s="13">
         <v>0</v>
       </c>
     </row>
@@ -3519,14 +3519,14 @@
       <c r="C109" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="D109" s="13">
+      <c r="D109" s="12">
         <v>6.34</v>
       </c>
       <c r="E109" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="F109" s="12">
-        <v>93</v>
+      <c r="F109" s="13">
+        <v>89</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
@@ -3539,14 +3539,14 @@
       <c r="C110" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="D110" s="13">
+      <c r="D110" s="12">
         <v>10.55</v>
       </c>
       <c r="E110" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="F110" s="12">
-        <v>67</v>
+      <c r="F110" s="13">
+        <v>66</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
@@ -3559,13 +3559,13 @@
       <c r="C111" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="D111" s="13">
+      <c r="D111" s="12">
         <v>10.55</v>
       </c>
       <c r="E111" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="F111" s="12">
+      <c r="F111" s="13">
         <v>0</v>
       </c>
     </row>
@@ -3579,14 +3579,14 @@
       <c r="C112" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="D112" s="13">
+      <c r="D112" s="12">
         <v>10.55</v>
       </c>
       <c r="E112" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="F112" s="12">
-        <v>11</v>
+      <c r="F112" s="13">
+        <v>26</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
@@ -3599,14 +3599,14 @@
       <c r="C113" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="D113" s="13">
+      <c r="D113" s="12">
         <v>6</v>
       </c>
       <c r="E113" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="F113" s="12">
-        <v>9</v>
+      <c r="F113" s="13">
+        <v>3</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
@@ -3619,13 +3619,13 @@
       <c r="C114" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="D114" s="13">
+      <c r="D114" s="12">
         <v>7.57</v>
       </c>
       <c r="E114" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="F114" s="12">
+      <c r="F114" s="13">
         <v>8</v>
       </c>
     </row>
@@ -3636,13 +3636,13 @@
       <c r="C115" s="6" t="s">
         <v>265</v>
       </c>
-      <c r="D115" s="13">
+      <c r="D115" s="12">
         <v>6.61</v>
       </c>
       <c r="E115" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="F115" s="12">
+      <c r="F115" s="13">
         <v>20</v>
       </c>
     </row>
@@ -3651,13 +3651,13 @@
         <v>95</v>
       </c>
       <c r="C116" s="6"/>
-      <c r="D116" s="13">
+      <c r="D116" s="12">
         <v>10.89</v>
       </c>
       <c r="E116" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="F116" s="12">
+      <c r="F116" s="13">
         <v>0</v>
       </c>
     </row>
@@ -3668,13 +3668,13 @@
       <c r="C117" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="D117" s="13">
+      <c r="D117" s="12">
         <v>9.17</v>
       </c>
       <c r="E117" s="8" t="s">
         <v>225</v>
       </c>
-      <c r="F117" s="12">
+      <c r="F117" s="13">
         <v>12</v>
       </c>
     </row>
@@ -3685,13 +3685,13 @@
       <c r="C118" s="6" t="s">
         <v>265</v>
       </c>
-      <c r="D118" s="13">
+      <c r="D118" s="12">
         <v>10.65</v>
       </c>
       <c r="E118" s="8" t="s">
         <v>227</v>
       </c>
-      <c r="F118" s="12">
+      <c r="F118" s="13">
         <v>13</v>
       </c>
     </row>
@@ -3702,13 +3702,13 @@
       <c r="C119" s="6" t="s">
         <v>280</v>
       </c>
-      <c r="D119" s="13">
+      <c r="D119" s="12">
         <v>36.090000000000003</v>
       </c>
       <c r="E119" s="8" t="s">
         <v>229</v>
       </c>
-      <c r="F119" s="12">
+      <c r="F119" s="13">
         <v>2</v>
       </c>
     </row>
@@ -3722,14 +3722,14 @@
       <c r="C120" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="D120" s="13">
+      <c r="D120" s="12">
         <v>4.1900000000000004</v>
       </c>
       <c r="E120" s="8" t="s">
         <v>231</v>
       </c>
-      <c r="F120" s="12">
-        <v>23</v>
+      <c r="F120" s="13">
+        <v>37</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
@@ -3742,13 +3742,13 @@
       <c r="C121" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="D121" s="13">
+      <c r="D121" s="12">
         <v>5.37</v>
       </c>
       <c r="E121" s="8" t="s">
         <v>233</v>
       </c>
-      <c r="F121" s="12">
+      <c r="F121" s="13">
         <v>8</v>
       </c>
     </row>
@@ -3762,14 +3762,14 @@
       <c r="C122" s="6" t="s">
         <v>257</v>
       </c>
-      <c r="D122" s="13">
+      <c r="D122" s="12">
         <v>5.64</v>
       </c>
       <c r="E122" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="F122" s="12">
-        <v>68</v>
+      <c r="F122" s="13">
+        <v>67</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
@@ -3782,13 +3782,13 @@
       <c r="C123" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="D123" s="13">
+      <c r="D123" s="12">
         <v>6.87</v>
       </c>
       <c r="E123" s="8" t="s">
         <v>237</v>
       </c>
-      <c r="F123" s="12">
+      <c r="F123" s="13">
         <v>24</v>
       </c>
     </row>
@@ -3802,13 +3802,13 @@
       <c r="C124" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="D124" s="13">
+      <c r="D124" s="12">
         <v>6.34</v>
       </c>
       <c r="E124" s="8" t="s">
         <v>239</v>
       </c>
-      <c r="F124" s="12">
+      <c r="F124" s="13">
         <v>25</v>
       </c>
     </row>
@@ -3822,13 +3822,13 @@
       <c r="C125" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="D125" s="13">
+      <c r="D125" s="12">
         <v>12.1</v>
       </c>
       <c r="E125" s="8" t="s">
         <v>241</v>
       </c>
-      <c r="F125" s="12">
+      <c r="F125" s="13">
         <v>130</v>
       </c>
     </row>
@@ -3842,13 +3842,13 @@
       <c r="C126" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="D126" s="13">
+      <c r="D126" s="12">
         <v>12.1</v>
       </c>
       <c r="E126" s="8" t="s">
         <v>243</v>
       </c>
-      <c r="F126" s="12">
+      <c r="F126" s="13">
         <v>51</v>
       </c>
     </row>
@@ -3862,13 +3862,13 @@
       <c r="C127" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="D127" s="13">
+      <c r="D127" s="12">
         <v>12.1</v>
       </c>
       <c r="E127" s="8">
         <v>43123133</v>
       </c>
-      <c r="F127" s="12">
+      <c r="F127" s="13">
         <v>27</v>
       </c>
     </row>

--- a/prix/pex.xlsx
+++ b/prix/pex.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\raccords-plomberie\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8743696D-4E8A-44E5-8055-EE199887F120}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F672B00A-B61A-433E-B50E-84DA652D2D23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{C27940F6-7049-4028-8D53-A9BC0C24D70B}"/>
   </bookViews>
@@ -1485,7 +1485,7 @@
         <v>43122970</v>
       </c>
       <c r="F2" s="13">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -1545,7 +1545,7 @@
         <v>5</v>
       </c>
       <c r="F5" s="13">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
@@ -1605,7 +1605,7 @@
         <v>11</v>
       </c>
       <c r="F8" s="13">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
@@ -1864,7 +1864,7 @@
         <v>38</v>
       </c>
       <c r="F22" s="13">
-        <v>354</v>
+        <v>321</v>
       </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.3">
@@ -1930,7 +1930,7 @@
         <v>46</v>
       </c>
       <c r="F26" s="13">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.3">
@@ -1996,7 +1996,7 @@
         <v>54</v>
       </c>
       <c r="F30" s="13">
-        <v>3.0000000000000133</v>
+        <v>2.0000000000000133</v>
       </c>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.3">
@@ -2099,7 +2099,7 @@
         <v>43123030</v>
       </c>
       <c r="F36" s="13">
-        <v>135</v>
+        <v>106</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
@@ -2139,7 +2139,7 @@
         <v>68</v>
       </c>
       <c r="F38" s="13">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
@@ -2159,7 +2159,7 @@
         <v>70</v>
       </c>
       <c r="F39" s="13">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
@@ -2179,7 +2179,7 @@
         <v>72</v>
       </c>
       <c r="F40" s="13">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
@@ -2199,7 +2199,7 @@
         <v>74</v>
       </c>
       <c r="F41" s="13">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
@@ -2279,7 +2279,7 @@
         <v>82</v>
       </c>
       <c r="F45" s="13">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
@@ -2299,7 +2299,7 @@
         <v>84</v>
       </c>
       <c r="F46" s="13">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
@@ -2377,7 +2377,7 @@
         <v>92</v>
       </c>
       <c r="F50" s="13">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
@@ -2525,7 +2525,7 @@
         <v>108</v>
       </c>
       <c r="F58" s="13">
-        <v>18</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
@@ -2581,7 +2581,7 @@
         <v>114</v>
       </c>
       <c r="F61" s="13">
-        <v>2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
@@ -2601,7 +2601,7 @@
         <v>116</v>
       </c>
       <c r="F62" s="13">
-        <v>6</v>
+        <v>49</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
@@ -2692,7 +2692,7 @@
         <v>126</v>
       </c>
       <c r="F67" s="13">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
@@ -2752,7 +2752,7 @@
         <v>132</v>
       </c>
       <c r="F70" s="13">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
@@ -2789,7 +2789,7 @@
         <v>136</v>
       </c>
       <c r="F72" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
@@ -2826,7 +2826,7 @@
         <v>140</v>
       </c>
       <c r="F74" s="13">
-        <v>101</v>
+        <v>91</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
@@ -2846,7 +2846,7 @@
         <v>142</v>
       </c>
       <c r="F75" s="13">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
@@ -2866,7 +2866,7 @@
         <v>144</v>
       </c>
       <c r="F76" s="13">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
@@ -3066,7 +3066,7 @@
         <v>164</v>
       </c>
       <c r="F86" s="13">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
@@ -3126,7 +3126,7 @@
         <v>170</v>
       </c>
       <c r="F89" s="13">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
@@ -3186,7 +3186,7 @@
         <v>176</v>
       </c>
       <c r="F92" s="13">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
@@ -3226,7 +3226,7 @@
         <v>180</v>
       </c>
       <c r="F94" s="13">
-        <v>23</v>
+        <v>3</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
@@ -3326,7 +3326,7 @@
         <v>190</v>
       </c>
       <c r="F99" s="13">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
@@ -3729,7 +3729,7 @@
         <v>231</v>
       </c>
       <c r="F120" s="13">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">

--- a/prix/pex.xlsx
+++ b/prix/pex.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\raccords-plomberie\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F672B00A-B61A-433E-B50E-84DA652D2D23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A0326E1-4C6A-40D7-B212-8F0872246739}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{C27940F6-7049-4028-8D53-A9BC0C24D70B}"/>
   </bookViews>
@@ -1054,7 +1054,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1086,6 +1086,9 @@
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1462,7 +1465,7 @@
       <c r="F1" s="10" t="s">
         <v>314</v>
       </c>
-      <c r="G1" s="1"/>
+      <c r="G1" s="12"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
@@ -1478,15 +1481,16 @@
       <c r="C2" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="D2" s="12">
+      <c r="D2" s="13">
         <v>5.49</v>
       </c>
       <c r="E2" s="8">
         <v>43122970</v>
       </c>
-      <c r="F2" s="13">
+      <c r="F2" s="14">
         <v>19</v>
       </c>
+      <c r="G2" s="12"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
@@ -1498,15 +1502,16 @@
       <c r="C3" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="D3" s="12">
+      <c r="D3" s="13">
         <v>8.8000000000000007</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="13">
-        <v>31</v>
-      </c>
+      <c r="F3" s="14">
+        <v>27</v>
+      </c>
+      <c r="G3" s="12"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
@@ -1518,15 +1523,16 @@
       <c r="C4" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="13">
         <v>11.68</v>
       </c>
       <c r="E4" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="13">
-        <v>10</v>
-      </c>
+      <c r="F4" s="14">
+        <v>9</v>
+      </c>
+      <c r="G4" s="12"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
@@ -1538,15 +1544,16 @@
       <c r="C5" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="13">
         <v>5.23</v>
       </c>
       <c r="E5" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="14">
         <v>31</v>
       </c>
+      <c r="G5" s="12"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
@@ -1558,15 +1565,16 @@
       <c r="C6" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="13">
         <v>8.2799999999999994</v>
       </c>
       <c r="E6" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="F6" s="13">
-        <v>12</v>
-      </c>
+      <c r="F6" s="14">
+        <v>9</v>
+      </c>
+      <c r="G6" s="12"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
@@ -1578,15 +1586,16 @@
       <c r="C7" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="13">
         <v>10.97</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="14">
         <v>5</v>
       </c>
+      <c r="G7" s="12"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
@@ -1598,15 +1607,16 @@
       <c r="C8" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="13">
         <v>4.9000000000000004</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="14">
         <v>222</v>
       </c>
+      <c r="G8" s="12"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
@@ -1618,15 +1628,16 @@
       <c r="C9" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="13">
         <v>5.28</v>
       </c>
       <c r="E9" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="14">
         <v>86</v>
       </c>
+      <c r="G9" s="12"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
@@ -1638,15 +1649,16 @@
       <c r="C10" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="13">
         <v>8.6</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="13">
+      <c r="F10" s="14">
         <v>90</v>
       </c>
+      <c r="G10" s="12"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
@@ -1658,15 +1670,16 @@
       <c r="C11" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="13">
         <v>2.2000000000000002</v>
       </c>
       <c r="E11" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="F11" s="13">
-        <v>49</v>
-      </c>
+      <c r="F11" s="14">
+        <v>31</v>
+      </c>
+      <c r="G11" s="12"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
@@ -1678,15 +1691,16 @@
       <c r="C12" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="D12" s="12">
+      <c r="D12" s="13">
         <v>7.19</v>
       </c>
       <c r="E12" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F12" s="13">
-        <v>43</v>
-      </c>
+      <c r="F12" s="14">
+        <v>38</v>
+      </c>
+      <c r="G12" s="12"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
@@ -1698,15 +1712,16 @@
       <c r="C13" s="6" t="s">
         <v>257</v>
       </c>
-      <c r="D13" s="12">
+      <c r="D13" s="13">
         <v>5.94</v>
       </c>
       <c r="E13" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="14">
         <v>58</v>
       </c>
+      <c r="G13" s="12"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
@@ -1718,15 +1733,16 @@
       <c r="C14" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="D14" s="12">
+      <c r="D14" s="13">
         <v>8.1999999999999993</v>
       </c>
       <c r="E14" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="F14" s="13">
-        <v>54</v>
-      </c>
+      <c r="F14" s="14">
+        <v>53</v>
+      </c>
+      <c r="G14" s="12"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
@@ -1738,15 +1754,16 @@
       <c r="C15" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="D15" s="12">
+      <c r="D15" s="13">
         <v>9.4500000000000011</v>
       </c>
       <c r="E15" s="8">
         <v>43122988</v>
       </c>
-      <c r="F15" s="13">
+      <c r="F15" s="14">
         <v>12</v>
       </c>
+      <c r="G15" s="12"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B16" s="6" t="s">
@@ -1755,334 +1772,354 @@
       <c r="C16" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="D16" s="12">
+      <c r="D16" s="13">
         <v>76.790000000000006</v>
       </c>
       <c r="E16" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="F16" s="13">
+      <c r="F16" s="14">
         <v>12</v>
       </c>
-    </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="G16" s="12"/>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B17" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="D17" s="12">
+      <c r="D17" s="13">
         <v>76.790000000000006</v>
       </c>
       <c r="E17" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="F17" s="13">
+      <c r="F17" s="14">
         <v>14.800000000000002</v>
       </c>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="G17" s="12"/>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B18" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="D18" s="12">
+      <c r="D18" s="13">
         <v>106.87</v>
       </c>
       <c r="E18" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F18" s="13">
+      <c r="F18" s="14">
         <v>6</v>
       </c>
-    </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="G18" s="12"/>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B19" s="6" t="s">
         <v>33</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="D19" s="12">
+      <c r="D19" s="13">
         <v>106.87</v>
       </c>
       <c r="E19" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F19" s="13">
+      <c r="F19" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="G19" s="12"/>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B20" s="6" t="s">
         <v>35</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>281</v>
       </c>
-      <c r="D20" s="12">
+      <c r="D20" s="13">
         <v>76.790000000000006</v>
       </c>
       <c r="E20" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="F20" s="13">
+      <c r="F20" s="14">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="G20" s="12"/>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B21" s="6" t="s">
         <v>37</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>281</v>
       </c>
-      <c r="D21" s="12">
+      <c r="D21" s="13">
         <v>76.790000000000006</v>
       </c>
       <c r="E21" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="F21" s="13">
+      <c r="F21" s="14">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="G21" s="12"/>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B22" s="6" t="s">
         <v>39</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="D22" s="12">
+      <c r="D22" s="13">
         <v>2.0100000000000002</v>
       </c>
       <c r="E22" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="F22" s="13">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="F22" s="14">
+        <v>71</v>
+      </c>
+      <c r="G22" s="12"/>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B23" s="6" t="s">
         <v>41</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="D23" s="12">
+      <c r="D23" s="13">
         <v>3.75</v>
       </c>
       <c r="E23" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F23" s="13">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="F23" s="14">
+        <v>189</v>
+      </c>
+      <c r="G23" s="12"/>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B24" s="6" t="s">
         <v>43</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="D24" s="12">
+      <c r="D24" s="13">
         <v>7.07</v>
       </c>
       <c r="E24" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="F24" s="13">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="F24" s="14">
+        <v>64</v>
+      </c>
+      <c r="G24" s="12"/>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B25" s="6" t="s">
         <v>45</v>
       </c>
       <c r="C25" s="6"/>
-      <c r="D25" s="12">
+      <c r="D25" s="13">
         <v>12.200000000000001</v>
       </c>
       <c r="E25" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="F25" s="13">
+      <c r="F25" s="14">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="G25" s="12"/>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B26" s="6" t="s">
         <v>47</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>272</v>
       </c>
-      <c r="D26" s="12">
+      <c r="D26" s="13">
         <v>8.35</v>
       </c>
       <c r="E26" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="F26" s="13">
+      <c r="F26" s="14">
         <v>-2</v>
       </c>
-    </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="G26" s="12"/>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B27" s="6" t="s">
         <v>49</v>
       </c>
       <c r="C27" s="6"/>
-      <c r="D27" s="12">
+      <c r="D27" s="13">
         <v>208.51</v>
       </c>
       <c r="E27" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="F27" s="13">
+      <c r="F27" s="14">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="G27" s="12"/>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B28" s="6" t="s">
         <v>51</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="D28" s="12">
+      <c r="D28" s="13">
         <v>157.20000000000002</v>
       </c>
       <c r="E28" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="F28" s="13">
+      <c r="F28" s="14">
         <v>3</v>
       </c>
-    </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="G28" s="12"/>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B29" s="6" t="s">
         <v>53</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="D29" s="12">
+      <c r="D29" s="13">
         <v>53.43</v>
       </c>
       <c r="E29" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="F29" s="13">
+      <c r="F29" s="14">
         <v>-1.0000000000000124</v>
       </c>
-    </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="G29" s="12"/>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B30" s="6" t="s">
         <v>55</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="D30" s="12">
+      <c r="D30" s="13">
         <v>106.87</v>
       </c>
       <c r="E30" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="F30" s="13">
+      <c r="F30" s="14">
         <v>2.0000000000000133</v>
       </c>
-    </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="G30" s="12"/>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B31" s="6" t="s">
         <v>57</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="D31" s="12">
+      <c r="D31" s="13">
         <v>53.43</v>
       </c>
       <c r="E31" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="F31" s="13">
+      <c r="F31" s="14">
         <v>-1.2434497875801753E-14</v>
       </c>
-    </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="G31" s="12"/>
+    </row>
+    <row r="32" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B32" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="D32" s="12">
+      <c r="D32" s="13">
         <v>106.87</v>
       </c>
       <c r="E32" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="F32" s="13">
-        <v>2.600000000000021</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F32" s="14">
+        <v>1.600000000000021</v>
+      </c>
+      <c r="G32" s="12"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B33" s="6" t="s">
         <v>61</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="D33" s="12">
+      <c r="D33" s="13">
         <v>158.75</v>
       </c>
       <c r="E33" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="F33" s="13">
+      <c r="F33" s="14">
         <v>249</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G33" s="12"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B34" s="6" t="s">
         <v>63</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>273</v>
       </c>
-      <c r="D34" s="12">
+      <c r="D34" s="13">
         <v>3.17</v>
       </c>
       <c r="E34" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="F34" s="13">
+      <c r="F34" s="14">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G34" s="12"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B35" s="6" t="s">
         <v>64</v>
       </c>
       <c r="C35" s="6"/>
-      <c r="D35" s="12">
+      <c r="D35" s="13">
         <v>45.910000000000004</v>
       </c>
       <c r="E35" s="8">
         <v>43123024</v>
       </c>
-      <c r="F35" s="13">
+      <c r="F35" s="14">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G35" s="12"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
         <v>292</v>
       </c>
@@ -2092,17 +2129,18 @@
       <c r="C36" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="D36" s="12">
+      <c r="D36" s="13">
         <v>3.61</v>
       </c>
       <c r="E36" s="8">
         <v>43123030</v>
       </c>
-      <c r="F36" s="13">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F36" s="14">
+        <v>91</v>
+      </c>
+      <c r="G36" s="12"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
         <v>292</v>
       </c>
@@ -2112,17 +2150,18 @@
       <c r="C37" s="6" t="s">
         <v>257</v>
       </c>
-      <c r="D37" s="12">
+      <c r="D37" s="13">
         <v>5.8</v>
       </c>
       <c r="E37" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="F37" s="13">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F37" s="14">
+        <v>15</v>
+      </c>
+      <c r="G37" s="12"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
         <v>292</v>
       </c>
@@ -2132,17 +2171,18 @@
       <c r="C38" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="D38" s="12">
+      <c r="D38" s="13">
         <v>5.93</v>
       </c>
       <c r="E38" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="F38" s="13">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F38" s="14">
+        <v>39</v>
+      </c>
+      <c r="G38" s="12"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
         <v>292</v>
       </c>
@@ -2152,17 +2192,18 @@
       <c r="C39" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="D39" s="12">
+      <c r="D39" s="13">
         <v>5.71</v>
       </c>
       <c r="E39" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="F39" s="13">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F39" s="14">
+        <v>16</v>
+      </c>
+      <c r="G39" s="12"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
         <v>292</v>
       </c>
@@ -2172,17 +2213,18 @@
       <c r="C40" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="D40" s="12">
+      <c r="D40" s="13">
         <v>9.7200000000000006</v>
       </c>
       <c r="E40" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="F40" s="13">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F40" s="14">
+        <v>8</v>
+      </c>
+      <c r="G40" s="12"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
         <v>291</v>
       </c>
@@ -2192,17 +2234,18 @@
       <c r="C41" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="D41" s="12">
+      <c r="D41" s="13">
         <v>4.6900000000000004</v>
       </c>
       <c r="E41" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="F41" s="13">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F41" s="14">
+        <v>29</v>
+      </c>
+      <c r="G41" s="12"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
         <v>291</v>
       </c>
@@ -2212,17 +2255,18 @@
       <c r="C42" s="6" t="s">
         <v>257</v>
       </c>
-      <c r="D42" s="12">
+      <c r="D42" s="13">
         <v>5.49</v>
       </c>
       <c r="E42" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="F42" s="13">
+      <c r="F42" s="14">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G42" s="12"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
         <v>291</v>
       </c>
@@ -2232,17 +2276,18 @@
       <c r="C43" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="D43" s="12">
+      <c r="D43" s="13">
         <v>6.0600000000000005</v>
       </c>
       <c r="E43" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="F43" s="13">
+      <c r="F43" s="14">
         <v>9</v>
       </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G43" s="12"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
         <v>291</v>
       </c>
@@ -2252,17 +2297,18 @@
       <c r="C44" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="D44" s="12">
+      <c r="D44" s="13">
         <v>6.22</v>
       </c>
       <c r="E44" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="F44" s="13">
+      <c r="F44" s="14">
         <v>38</v>
       </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G44" s="12"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
         <v>291</v>
       </c>
@@ -2272,17 +2318,18 @@
       <c r="C45" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="D45" s="12">
+      <c r="D45" s="13">
         <v>9.64</v>
       </c>
       <c r="E45" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="F45" s="13">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F45" s="14">
+        <v>10</v>
+      </c>
+      <c r="G45" s="12"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
         <v>296</v>
       </c>
@@ -2292,17 +2339,18 @@
       <c r="C46" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="D46" s="12">
+      <c r="D46" s="13">
         <v>8.69</v>
       </c>
       <c r="E46" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="F46" s="13">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F46" s="14">
+        <v>-8</v>
+      </c>
+      <c r="G46" s="12"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
         <v>296</v>
       </c>
@@ -2310,17 +2358,18 @@
         <v>87</v>
       </c>
       <c r="C47" s="6"/>
-      <c r="D47" s="12">
+      <c r="D47" s="13">
         <v>11.8</v>
       </c>
       <c r="E47" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="F47" s="13">
+      <c r="F47" s="14">
         <v>35</v>
       </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G47" s="12"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
         <v>296</v>
       </c>
@@ -2330,17 +2379,18 @@
       <c r="C48" s="6" t="s">
         <v>271</v>
       </c>
-      <c r="D48" s="12">
+      <c r="D48" s="13">
         <v>18.05</v>
       </c>
       <c r="E48" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="F48" s="13">
+      <c r="F48" s="14">
         <v>33</v>
       </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G48" s="12"/>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
         <v>293</v>
       </c>
@@ -2350,17 +2400,18 @@
       <c r="C49" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="D49" s="12">
+      <c r="D49" s="13">
         <v>8.370000000000001</v>
       </c>
       <c r="E49" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="F49" s="13">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F49" s="14">
+        <v>19</v>
+      </c>
+      <c r="G49" s="12"/>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
         <v>293</v>
       </c>
@@ -2370,47 +2421,50 @@
       <c r="C50" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="D50" s="12">
+      <c r="D50" s="13">
         <v>15.88</v>
       </c>
       <c r="E50" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="F50" s="13">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F50" s="14">
+        <v>39</v>
+      </c>
+      <c r="G50" s="12"/>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B51" s="6" t="s">
         <v>95</v>
       </c>
       <c r="C51" s="6"/>
-      <c r="D51" s="12">
+      <c r="D51" s="13">
         <v>9.75</v>
       </c>
       <c r="E51" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="F51" s="13">
+      <c r="F51" s="14">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G51" s="12"/>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B52" s="6" t="s">
         <v>97</v>
       </c>
       <c r="C52" s="6"/>
-      <c r="D52" s="12">
+      <c r="D52" s="13">
         <v>11.08</v>
       </c>
       <c r="E52" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="F52" s="13">
+      <c r="F52" s="14">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G52" s="12"/>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="5" t="s">
         <v>294</v>
       </c>
@@ -2420,17 +2474,18 @@
       <c r="C53" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="D53" s="12">
+      <c r="D53" s="13">
         <v>17.21</v>
       </c>
       <c r="E53" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="F53" s="13">
+      <c r="F53" s="14">
         <v>9</v>
       </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G53" s="12"/>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="5" t="s">
         <v>294</v>
       </c>
@@ -2440,17 +2495,18 @@
       <c r="C54" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="D54" s="12">
+      <c r="D54" s="13">
         <v>13.66</v>
       </c>
       <c r="E54" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="F54" s="13">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F54" s="14">
+        <v>21</v>
+      </c>
+      <c r="G54" s="12"/>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="5" t="s">
         <v>295</v>
       </c>
@@ -2460,17 +2516,18 @@
       <c r="C55" s="6" t="s">
         <v>261</v>
       </c>
-      <c r="D55" s="12">
+      <c r="D55" s="13">
         <v>13.88</v>
       </c>
       <c r="E55" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="F55" s="13">
+      <c r="F55" s="14">
         <v>18</v>
       </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G55" s="12"/>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="5" t="s">
         <v>295</v>
       </c>
@@ -2480,17 +2537,18 @@
       <c r="C56" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="D56" s="12">
+      <c r="D56" s="13">
         <v>21.26</v>
       </c>
       <c r="E56" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="F56" s="13">
+      <c r="F56" s="14">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G56" s="12"/>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="5" t="s">
         <v>295</v>
       </c>
@@ -2500,17 +2558,18 @@
       <c r="C57" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="D57" s="12">
+      <c r="D57" s="13">
         <v>21.26</v>
       </c>
       <c r="E57" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="F57" s="13">
+      <c r="F57" s="14">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G57" s="12"/>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="5" t="s">
         <v>289</v>
       </c>
@@ -2518,17 +2577,18 @@
         <v>109</v>
       </c>
       <c r="C58" s="6"/>
-      <c r="D58" s="12">
+      <c r="D58" s="13">
         <v>6.15</v>
       </c>
       <c r="E58" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="F58" s="13">
-        <v>-4</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F58" s="14">
+        <v>36</v>
+      </c>
+      <c r="G58" s="12"/>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="5" t="s">
         <v>289</v>
       </c>
@@ -2536,17 +2596,18 @@
         <v>111</v>
       </c>
       <c r="C59" s="6"/>
-      <c r="D59" s="12">
+      <c r="D59" s="13">
         <v>9.99</v>
       </c>
       <c r="E59" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="F59" s="13">
+      <c r="F59" s="14">
         <v>13</v>
       </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G59" s="12"/>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="5" t="s">
         <v>289</v>
       </c>
@@ -2554,17 +2615,18 @@
         <v>113</v>
       </c>
       <c r="C60" s="6"/>
-      <c r="D60" s="12">
+      <c r="D60" s="13">
         <v>15.49</v>
       </c>
       <c r="E60" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="F60" s="13">
+      <c r="F60" s="14">
         <v>8</v>
       </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G60" s="12"/>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
         <v>286</v>
       </c>
@@ -2574,17 +2636,18 @@
       <c r="C61" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="D61" s="12">
+      <c r="D61" s="13">
         <v>20.34</v>
       </c>
       <c r="E61" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="F61" s="13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F61" s="14">
+        <v>-9</v>
+      </c>
+      <c r="G61" s="12"/>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="5" t="s">
         <v>287</v>
       </c>
@@ -2594,17 +2657,18 @@
       <c r="C62" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="D62" s="12">
+      <c r="D62" s="13">
         <v>6.92</v>
       </c>
       <c r="E62" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="F62" s="13">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F62" s="14">
+        <v>42</v>
+      </c>
+      <c r="G62" s="12"/>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" s="5" t="s">
         <v>287</v>
       </c>
@@ -2614,68 +2678,72 @@
       <c r="C63" s="6" t="s">
         <v>257</v>
       </c>
-      <c r="D63" s="12">
+      <c r="D63" s="13">
         <v>8.39</v>
       </c>
       <c r="E63" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="F63" s="13">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F63" s="14">
+        <v>9</v>
+      </c>
+      <c r="G63" s="12"/>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B64" s="6" t="s">
         <v>121</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="D64" s="12">
+      <c r="D64" s="13">
         <v>4.4000000000000004</v>
       </c>
       <c r="E64" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="F64" s="13">
+      <c r="F64" s="14">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G64" s="12"/>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B65" s="6" t="s">
         <v>123</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>275</v>
       </c>
-      <c r="D65" s="12">
+      <c r="D65" s="13">
         <v>9.99</v>
       </c>
       <c r="E65" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="F65" s="13">
+      <c r="F65" s="14">
         <v>2</v>
       </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G65" s="12"/>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B66" s="6" t="s">
         <v>125</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="D66" s="12">
+      <c r="D66" s="13">
         <v>9.99</v>
       </c>
       <c r="E66" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="F66" s="13">
+      <c r="F66" s="14">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G66" s="12"/>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" s="5" t="s">
         <v>288</v>
       </c>
@@ -2685,17 +2753,18 @@
       <c r="C67" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="D67" s="12">
+      <c r="D67" s="13">
         <v>5.53</v>
       </c>
       <c r="E67" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="F67" s="13">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F67" s="14">
+        <v>10</v>
+      </c>
+      <c r="G67" s="12"/>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" s="5" t="s">
         <v>288</v>
       </c>
@@ -2705,17 +2774,18 @@
       <c r="C68" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="D68" s="12">
+      <c r="D68" s="13">
         <v>8.8000000000000007</v>
       </c>
       <c r="E68" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="F68" s="13">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F68" s="14">
+        <v>18</v>
+      </c>
+      <c r="G68" s="12"/>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" s="5" t="s">
         <v>288</v>
       </c>
@@ -2725,17 +2795,18 @@
       <c r="C69" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="D69" s="12">
+      <c r="D69" s="13">
         <v>13.77</v>
       </c>
       <c r="E69" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="F69" s="13">
+      <c r="F69" s="14">
         <v>12</v>
       </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G69" s="12"/>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" s="5" t="s">
         <v>282</v>
       </c>
@@ -2745,17 +2816,18 @@
       <c r="C70" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="D70" s="12">
+      <c r="D70" s="13">
         <v>4.71</v>
       </c>
       <c r="E70" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="F70" s="13">
+      <c r="F70" s="14">
         <v>15</v>
       </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G70" s="12"/>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" s="5" t="s">
         <v>282</v>
       </c>
@@ -2765,51 +2837,54 @@
       <c r="C71" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="D71" s="12">
+      <c r="D71" s="13">
         <v>5.42</v>
       </c>
       <c r="E71" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="F71" s="13">
+      <c r="F71" s="14">
         <v>9</v>
       </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G71" s="12"/>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B72" s="6" t="s">
         <v>137</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D72" s="12">
+      <c r="D72" s="13">
         <v>1.6500000000000001</v>
       </c>
       <c r="E72" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="F72" s="13">
+      <c r="F72" s="14">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G72" s="12"/>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B73" s="6" t="s">
         <v>139</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D73" s="12">
+      <c r="D73" s="13">
         <v>1.6500000000000001</v>
       </c>
       <c r="E73" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="F73" s="13">
+      <c r="F73" s="14">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G73" s="12"/>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" s="5" t="s">
         <v>304</v>
       </c>
@@ -2819,17 +2894,18 @@
       <c r="C74" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="D74" s="12">
+      <c r="D74" s="13">
         <v>7.96</v>
       </c>
       <c r="E74" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="F74" s="13">
+      <c r="F74" s="14">
         <v>91</v>
       </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G74" s="12"/>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" s="5" t="s">
         <v>304</v>
       </c>
@@ -2839,17 +2915,18 @@
       <c r="C75" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="D75" s="12">
+      <c r="D75" s="13">
         <v>19.14</v>
       </c>
       <c r="E75" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="F75" s="13">
+      <c r="F75" s="14">
         <v>8</v>
       </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G75" s="12"/>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" s="5" t="s">
         <v>303</v>
       </c>
@@ -2859,17 +2936,18 @@
       <c r="C76" s="6" t="s">
         <v>279</v>
       </c>
-      <c r="D76" s="12">
+      <c r="D76" s="13">
         <v>23.35</v>
       </c>
       <c r="E76" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="F76" s="13">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F76" s="14">
+        <v>13</v>
+      </c>
+      <c r="G76" s="12"/>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" s="5" t="s">
         <v>311</v>
       </c>
@@ -2879,17 +2957,18 @@
       <c r="C77" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="D77" s="12">
+      <c r="D77" s="13">
         <v>9.9700000000000006</v>
       </c>
       <c r="E77" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="F77" s="13">
+      <c r="F77" s="14">
         <v>20</v>
       </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G77" s="12"/>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" s="5" t="s">
         <v>311</v>
       </c>
@@ -2899,17 +2978,18 @@
       <c r="C78" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="D78" s="12">
+      <c r="D78" s="13">
         <v>10.620000000000001</v>
       </c>
       <c r="E78" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="F78" s="13">
+      <c r="F78" s="14">
         <v>13</v>
       </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G78" s="12"/>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" s="5" t="s">
         <v>311</v>
       </c>
@@ -2919,17 +2999,18 @@
       <c r="C79" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="D79" s="12">
+      <c r="D79" s="13">
         <v>11.86</v>
       </c>
       <c r="E79" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="F79" s="13">
+      <c r="F79" s="14">
         <v>0</v>
       </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G79" s="12"/>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" s="5" t="s">
         <v>310</v>
       </c>
@@ -2939,17 +3020,18 @@
       <c r="C80" s="6" t="s">
         <v>265</v>
       </c>
-      <c r="D80" s="12">
+      <c r="D80" s="13">
         <v>10.55</v>
       </c>
       <c r="E80" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="F80" s="13">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F80" s="14">
+        <v>50</v>
+      </c>
+      <c r="G80" s="12"/>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" s="5" t="s">
         <v>310</v>
       </c>
@@ -2959,17 +3041,18 @@
       <c r="C81" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="D81" s="12">
+      <c r="D81" s="13">
         <v>12.63</v>
       </c>
       <c r="E81" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="F81" s="13">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F81" s="14">
+        <v>32</v>
+      </c>
+      <c r="G81" s="12"/>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" s="5" t="s">
         <v>310</v>
       </c>
@@ -2979,17 +3062,18 @@
       <c r="C82" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="D82" s="12">
+      <c r="D82" s="13">
         <v>13.89</v>
       </c>
       <c r="E82" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="F82" s="13">
+      <c r="F82" s="14">
         <v>9</v>
       </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G82" s="12"/>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" s="5" t="s">
         <v>313</v>
       </c>
@@ -2999,17 +3083,18 @@
       <c r="C83" s="6" t="s">
         <v>261</v>
       </c>
-      <c r="D83" s="12">
+      <c r="D83" s="13">
         <v>12.1</v>
       </c>
       <c r="E83" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="F83" s="13">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F83" s="14">
+        <v>32</v>
+      </c>
+      <c r="G83" s="12"/>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" s="5" t="s">
         <v>313</v>
       </c>
@@ -3019,17 +3104,18 @@
       <c r="C84" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="D84" s="12">
+      <c r="D84" s="13">
         <v>13.31</v>
       </c>
       <c r="E84" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="F84" s="13">
+      <c r="F84" s="14">
         <v>33</v>
       </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G84" s="12"/>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" s="5" t="s">
         <v>313</v>
       </c>
@@ -3039,17 +3125,18 @@
       <c r="C85" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="D85" s="12">
+      <c r="D85" s="13">
         <v>23.62</v>
       </c>
       <c r="E85" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="F85" s="13">
+      <c r="F85" s="14">
         <v>24</v>
       </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G85" s="12"/>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" s="5" t="s">
         <v>306</v>
       </c>
@@ -3059,17 +3146,18 @@
       <c r="C86" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="D86" s="12">
+      <c r="D86" s="13">
         <v>6.61</v>
       </c>
       <c r="E86" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="F86" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F86" s="14">
+        <v>20</v>
+      </c>
+      <c r="G86" s="12"/>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" s="5" t="s">
         <v>306</v>
       </c>
@@ -3079,17 +3167,18 @@
       <c r="C87" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="D87" s="12">
+      <c r="D87" s="13">
         <v>7.55</v>
       </c>
       <c r="E87" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="F87" s="13">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F87" s="14">
+        <v>23</v>
+      </c>
+      <c r="G87" s="12"/>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" s="5" t="s">
         <v>306</v>
       </c>
@@ -3099,17 +3188,18 @@
       <c r="C88" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="D88" s="12">
+      <c r="D88" s="13">
         <v>8.86</v>
       </c>
       <c r="E88" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="F88" s="13">
+      <c r="F88" s="14">
         <v>38</v>
       </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G88" s="12"/>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" s="5" t="s">
         <v>309</v>
       </c>
@@ -3119,17 +3209,18 @@
       <c r="C89" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="D89" s="12">
+      <c r="D89" s="13">
         <v>1.82</v>
       </c>
       <c r="E89" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="F89" s="13">
+      <c r="F89" s="14">
         <v>90</v>
       </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G89" s="12"/>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" s="5" t="s">
         <v>309</v>
       </c>
@@ -3139,17 +3230,18 @@
       <c r="C90" s="6" t="s">
         <v>257</v>
       </c>
-      <c r="D90" s="12">
+      <c r="D90" s="13">
         <v>4.8899999999999997</v>
       </c>
       <c r="E90" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="F90" s="13">
+      <c r="F90" s="14">
         <v>76</v>
       </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G90" s="12"/>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" s="5" t="s">
         <v>309</v>
       </c>
@@ -3159,17 +3251,18 @@
       <c r="C91" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="D91" s="12">
+      <c r="D91" s="13">
         <v>5.42</v>
       </c>
       <c r="E91" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="F91" s="13">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F91" s="14">
+        <v>46</v>
+      </c>
+      <c r="G91" s="12"/>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" s="5" t="s">
         <v>309</v>
       </c>
@@ -3179,17 +3272,18 @@
       <c r="C92" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="D92" s="12">
+      <c r="D92" s="13">
         <v>5.1100000000000003</v>
       </c>
       <c r="E92" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="F92" s="13">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F92" s="14">
+        <v>47</v>
+      </c>
+      <c r="G92" s="12"/>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" s="5" t="s">
         <v>309</v>
       </c>
@@ -3199,17 +3293,18 @@
       <c r="C93" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="D93" s="12">
+      <c r="D93" s="13">
         <v>10.02</v>
       </c>
       <c r="E93" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="F93" s="13">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F93" s="14">
+        <v>6</v>
+      </c>
+      <c r="G93" s="12"/>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" s="5" t="s">
         <v>307</v>
       </c>
@@ -3219,17 +3314,18 @@
       <c r="C94" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="D94" s="12">
+      <c r="D94" s="13">
         <v>2.1800000000000002</v>
       </c>
       <c r="E94" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="F94" s="13">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F94" s="14">
+        <v>2</v>
+      </c>
+      <c r="G94" s="12"/>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" s="5" t="s">
         <v>307</v>
       </c>
@@ -3239,17 +3335,18 @@
       <c r="C95" s="6" t="s">
         <v>257</v>
       </c>
-      <c r="D95" s="12">
+      <c r="D95" s="13">
         <v>8.32</v>
       </c>
       <c r="E95" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="F95" s="13">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F95" s="14">
+        <v>75</v>
+      </c>
+      <c r="G95" s="12"/>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" s="5" t="s">
         <v>307</v>
       </c>
@@ -3259,17 +3356,18 @@
       <c r="C96" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="D96" s="12">
+      <c r="D96" s="13">
         <v>8.32</v>
       </c>
       <c r="E96" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="F96" s="13">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F96" s="14">
+        <v>83</v>
+      </c>
+      <c r="G96" s="12"/>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" s="5" t="s">
         <v>307</v>
       </c>
@@ -3279,17 +3377,18 @@
       <c r="C97" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="D97" s="12">
+      <c r="D97" s="13">
         <v>7.84</v>
       </c>
       <c r="E97" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="F97" s="13">
+      <c r="F97" s="14">
         <v>49</v>
       </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G97" s="12"/>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" s="5" t="s">
         <v>307</v>
       </c>
@@ -3299,17 +3398,18 @@
       <c r="C98" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="D98" s="12">
+      <c r="D98" s="13">
         <v>13.31</v>
       </c>
       <c r="E98" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="F98" s="13">
+      <c r="F98" s="14">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G98" s="12"/>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" s="5" t="s">
         <v>300</v>
       </c>
@@ -3319,17 +3419,18 @@
       <c r="C99" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="D99" s="12">
+      <c r="D99" s="13">
         <v>8.25</v>
       </c>
       <c r="E99" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="F99" s="13">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F99" s="14">
+        <v>79</v>
+      </c>
+      <c r="G99" s="12"/>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" s="5" t="s">
         <v>300</v>
       </c>
@@ -3339,17 +3440,18 @@
       <c r="C100" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="D100" s="12">
+      <c r="D100" s="13">
         <v>6.87</v>
       </c>
       <c r="E100" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="F100" s="13">
+      <c r="F100" s="14">
         <v>35</v>
       </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G100" s="12"/>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" s="5" t="s">
         <v>300</v>
       </c>
@@ -3359,17 +3461,18 @@
       <c r="C101" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="D101" s="12">
+      <c r="D101" s="13">
         <v>26.18</v>
       </c>
       <c r="E101" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="F101" s="13">
+      <c r="F101" s="14">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G101" s="12"/>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" s="5" t="s">
         <v>299</v>
       </c>
@@ -3379,17 +3482,18 @@
       <c r="C102" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="D102" s="12">
+      <c r="D102" s="13">
         <v>8.4700000000000006</v>
       </c>
       <c r="E102" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="F102" s="13">
+      <c r="F102" s="14">
         <v>106</v>
       </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G102" s="12"/>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" s="5" t="s">
         <v>299</v>
       </c>
@@ -3399,17 +3503,18 @@
       <c r="C103" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="D103" s="12">
+      <c r="D103" s="13">
         <v>9.6300000000000008</v>
       </c>
       <c r="E103" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="F103" s="13">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F103" s="14">
+        <v>31</v>
+      </c>
+      <c r="G103" s="12"/>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" s="5" t="s">
         <v>299</v>
       </c>
@@ -3419,17 +3524,18 @@
       <c r="C104" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="D104" s="12">
+      <c r="D104" s="13">
         <v>10.48</v>
       </c>
       <c r="E104" s="8" t="s">
         <v>200</v>
       </c>
-      <c r="F104" s="13">
+      <c r="F104" s="14">
         <v>29</v>
       </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G104" s="12"/>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" s="5" t="s">
         <v>302</v>
       </c>
@@ -3439,17 +3545,18 @@
       <c r="C105" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="D105" s="12">
+      <c r="D105" s="13">
         <v>6.61</v>
       </c>
       <c r="E105" s="8" t="s">
         <v>202</v>
       </c>
-      <c r="F105" s="13">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F105" s="14">
+        <v>51</v>
+      </c>
+      <c r="G105" s="12"/>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" s="5" t="s">
         <v>302</v>
       </c>
@@ -3459,17 +3566,18 @@
       <c r="C106" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="D106" s="12">
+      <c r="D106" s="13">
         <v>5.83</v>
       </c>
       <c r="E106" s="8" t="s">
         <v>204</v>
       </c>
-      <c r="F106" s="13">
+      <c r="F106" s="14">
         <v>21</v>
       </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G106" s="12"/>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" s="5" t="s">
         <v>302</v>
       </c>
@@ -3479,17 +3587,18 @@
       <c r="C107" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="D107" s="12">
+      <c r="D107" s="13">
         <v>5.83</v>
       </c>
       <c r="E107" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="F107" s="13">
+      <c r="F107" s="14">
         <v>3</v>
       </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G107" s="12"/>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" s="5" t="s">
         <v>302</v>
       </c>
@@ -3499,17 +3608,18 @@
       <c r="C108" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="D108" s="12">
+      <c r="D108" s="13">
         <v>13.02</v>
       </c>
       <c r="E108" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="F108" s="13">
+      <c r="F108" s="14">
         <v>0</v>
       </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G108" s="12"/>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" s="5" t="s">
         <v>301</v>
       </c>
@@ -3519,17 +3629,18 @@
       <c r="C109" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="D109" s="12">
+      <c r="D109" s="13">
         <v>6.34</v>
       </c>
       <c r="E109" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="F109" s="13">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F109" s="14">
+        <v>88</v>
+      </c>
+      <c r="G109" s="12"/>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" s="5" t="s">
         <v>301</v>
       </c>
@@ -3539,17 +3650,18 @@
       <c r="C110" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="D110" s="12">
+      <c r="D110" s="13">
         <v>10.55</v>
       </c>
       <c r="E110" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="F110" s="13">
+      <c r="F110" s="14">
         <v>66</v>
       </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G110" s="12"/>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" s="5" t="s">
         <v>301</v>
       </c>
@@ -3559,17 +3671,18 @@
       <c r="C111" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="D111" s="12">
+      <c r="D111" s="13">
         <v>10.55</v>
       </c>
       <c r="E111" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="F111" s="13">
+      <c r="F111" s="14">
         <v>0</v>
       </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G111" s="12"/>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" s="5" t="s">
         <v>301</v>
       </c>
@@ -3579,17 +3692,18 @@
       <c r="C112" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="D112" s="12">
+      <c r="D112" s="13">
         <v>10.55</v>
       </c>
       <c r="E112" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="F112" s="13">
+      <c r="F112" s="14">
         <v>26</v>
       </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G112" s="12"/>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" s="5" t="s">
         <v>298</v>
       </c>
@@ -3599,17 +3713,18 @@
       <c r="C113" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="D113" s="12">
+      <c r="D113" s="13">
         <v>6</v>
       </c>
       <c r="E113" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="F113" s="13">
+      <c r="F113" s="14">
         <v>3</v>
       </c>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G113" s="12"/>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" s="5" t="s">
         <v>298</v>
       </c>
@@ -3619,100 +3734,106 @@
       <c r="C114" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="D114" s="12">
+      <c r="D114" s="13">
         <v>7.57</v>
       </c>
       <c r="E114" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="F114" s="13">
+      <c r="F114" s="14">
         <v>8</v>
       </c>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G114" s="12"/>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B115" s="6" t="s">
         <v>223</v>
       </c>
       <c r="C115" s="6" t="s">
         <v>265</v>
       </c>
-      <c r="D115" s="12">
+      <c r="D115" s="13">
         <v>6.61</v>
       </c>
       <c r="E115" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="F115" s="13">
+      <c r="F115" s="14">
         <v>20</v>
       </c>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G115" s="12"/>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B116" s="6" t="s">
         <v>95</v>
       </c>
       <c r="C116" s="6"/>
-      <c r="D116" s="12">
+      <c r="D116" s="13">
         <v>10.89</v>
       </c>
       <c r="E116" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="F116" s="13">
+      <c r="F116" s="14">
         <v>0</v>
       </c>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G116" s="12"/>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B117" s="6" t="s">
         <v>226</v>
       </c>
       <c r="C117" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="D117" s="12">
+      <c r="D117" s="13">
         <v>9.17</v>
       </c>
       <c r="E117" s="8" t="s">
         <v>225</v>
       </c>
-      <c r="F117" s="13">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F117" s="14">
+        <v>11</v>
+      </c>
+      <c r="G117" s="12"/>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B118" s="6" t="s">
         <v>228</v>
       </c>
       <c r="C118" s="6" t="s">
         <v>265</v>
       </c>
-      <c r="D118" s="12">
+      <c r="D118" s="13">
         <v>10.65</v>
       </c>
       <c r="E118" s="8" t="s">
         <v>227</v>
       </c>
-      <c r="F118" s="13">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F118" s="14">
+        <v>12</v>
+      </c>
+      <c r="G118" s="12"/>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B119" s="6" t="s">
         <v>230</v>
       </c>
       <c r="C119" s="6" t="s">
         <v>280</v>
       </c>
-      <c r="D119" s="12">
+      <c r="D119" s="13">
         <v>36.090000000000003</v>
       </c>
       <c r="E119" s="8" t="s">
         <v>229</v>
       </c>
-      <c r="F119" s="13">
+      <c r="F119" s="14">
         <v>2</v>
       </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G119" s="12"/>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" s="5" t="s">
         <v>308</v>
       </c>
@@ -3722,17 +3843,18 @@
       <c r="C120" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="D120" s="12">
+      <c r="D120" s="13">
         <v>4.1900000000000004</v>
       </c>
       <c r="E120" s="8" t="s">
         <v>231</v>
       </c>
-      <c r="F120" s="13">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F120" s="14">
+        <v>32</v>
+      </c>
+      <c r="G120" s="12"/>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" s="5" t="s">
         <v>308</v>
       </c>
@@ -3742,17 +3864,18 @@
       <c r="C121" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="D121" s="12">
+      <c r="D121" s="13">
         <v>5.37</v>
       </c>
       <c r="E121" s="8" t="s">
         <v>233</v>
       </c>
-      <c r="F121" s="13">
+      <c r="F121" s="14">
         <v>8</v>
       </c>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G121" s="12"/>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" s="5" t="s">
         <v>308</v>
       </c>
@@ -3762,17 +3885,18 @@
       <c r="C122" s="6" t="s">
         <v>257</v>
       </c>
-      <c r="D122" s="12">
+      <c r="D122" s="13">
         <v>5.64</v>
       </c>
       <c r="E122" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="F122" s="13">
+      <c r="F122" s="14">
         <v>67</v>
       </c>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G122" s="12"/>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" s="5" t="s">
         <v>308</v>
       </c>
@@ -3782,17 +3906,18 @@
       <c r="C123" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="D123" s="12">
+      <c r="D123" s="13">
         <v>6.87</v>
       </c>
       <c r="E123" s="8" t="s">
         <v>237</v>
       </c>
-      <c r="F123" s="13">
+      <c r="F123" s="14">
         <v>24</v>
       </c>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G123" s="12"/>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" s="5" t="s">
         <v>308</v>
       </c>
@@ -3802,17 +3927,18 @@
       <c r="C124" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="D124" s="12">
+      <c r="D124" s="13">
         <v>6.34</v>
       </c>
       <c r="E124" s="8" t="s">
         <v>239</v>
       </c>
-      <c r="F124" s="13">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F124" s="14">
+        <v>23</v>
+      </c>
+      <c r="G124" s="12"/>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" s="5" t="s">
         <v>312</v>
       </c>
@@ -3822,17 +3948,18 @@
       <c r="C125" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="D125" s="12">
+      <c r="D125" s="13">
         <v>12.1</v>
       </c>
       <c r="E125" s="8" t="s">
         <v>241</v>
       </c>
-      <c r="F125" s="13">
+      <c r="F125" s="14">
         <v>130</v>
       </c>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G125" s="12"/>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" s="5" t="s">
         <v>312</v>
       </c>
@@ -3842,17 +3969,18 @@
       <c r="C126" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="D126" s="12">
+      <c r="D126" s="13">
         <v>12.1</v>
       </c>
       <c r="E126" s="8" t="s">
         <v>243</v>
       </c>
-      <c r="F126" s="13">
+      <c r="F126" s="14">
         <v>51</v>
       </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G126" s="12"/>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" s="5" t="s">
         <v>312</v>
       </c>
@@ -3862,17 +3990,18 @@
       <c r="C127" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="D127" s="12">
+      <c r="D127" s="13">
         <v>12.1</v>
       </c>
       <c r="E127" s="8">
         <v>43123133</v>
       </c>
-      <c r="F127" s="13">
+      <c r="F127" s="14">
         <v>27</v>
       </c>
-    </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G127" s="12"/>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128" s="5" t="s">
         <v>297</v>
       </c>

--- a/prix/pex.xlsx
+++ b/prix/pex.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\raccords-plomberie\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A0326E1-4C6A-40D7-B212-8F0872246739}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81558FF6-C4F7-4BC3-B2CF-260325C641FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{C27940F6-7049-4028-8D53-A9BC0C24D70B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="315">
   <si>
     <t>Pex coude 1/2F x16</t>
   </si>
@@ -981,9 +981,6 @@
   </si>
   <si>
     <t>disponible</t>
-  </si>
-  <si>
-    <t>0</t>
   </si>
 </sst>
 </file>
@@ -1054,7 +1051,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1087,13 +1084,10 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -1465,7 +1459,7 @@
       <c r="F1" s="10" t="s">
         <v>314</v>
       </c>
-      <c r="G1" s="12"/>
+      <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
@@ -1487,10 +1481,9 @@
       <c r="E2" s="8">
         <v>43122970</v>
       </c>
-      <c r="F2" s="14">
+      <c r="F2" s="12">
         <v>19</v>
       </c>
-      <c r="G2" s="12"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
@@ -1508,10 +1501,9 @@
       <c r="E3" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="14">
+      <c r="F3" s="12">
         <v>27</v>
       </c>
-      <c r="G3" s="12"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
@@ -1529,10 +1521,9 @@
       <c r="E4" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="14">
+      <c r="F4" s="12">
         <v>9</v>
       </c>
-      <c r="G4" s="12"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
@@ -1550,10 +1541,9 @@
       <c r="E5" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="14">
+      <c r="F5" s="12">
         <v>31</v>
       </c>
-      <c r="G5" s="12"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
@@ -1571,10 +1561,9 @@
       <c r="E6" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="F6" s="14">
+      <c r="F6" s="12">
         <v>9</v>
       </c>
-      <c r="G6" s="12"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
@@ -1592,10 +1581,9 @@
       <c r="E7" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="14">
+      <c r="F7" s="12">
         <v>5</v>
       </c>
-      <c r="G7" s="12"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
@@ -1613,10 +1601,9 @@
       <c r="E8" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="14">
+      <c r="F8" s="12">
         <v>222</v>
       </c>
-      <c r="G8" s="12"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
@@ -1634,10 +1621,9 @@
       <c r="E9" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F9" s="14">
+      <c r="F9" s="12">
         <v>86</v>
       </c>
-      <c r="G9" s="12"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
@@ -1655,10 +1641,9 @@
       <c r="E10" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="14">
+      <c r="F10" s="12">
         <v>90</v>
       </c>
-      <c r="G10" s="12"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
@@ -1676,10 +1661,9 @@
       <c r="E11" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="F11" s="14">
+      <c r="F11" s="12">
         <v>31</v>
       </c>
-      <c r="G11" s="12"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
@@ -1697,10 +1681,9 @@
       <c r="E12" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F12" s="14">
+      <c r="F12" s="12">
         <v>38</v>
       </c>
-      <c r="G12" s="12"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
@@ -1718,10 +1701,9 @@
       <c r="E13" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="F13" s="14">
+      <c r="F13" s="12">
         <v>58</v>
       </c>
-      <c r="G13" s="12"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
@@ -1739,10 +1721,9 @@
       <c r="E14" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="F14" s="14">
+      <c r="F14" s="12">
         <v>53</v>
       </c>
-      <c r="G14" s="12"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
@@ -1760,10 +1741,9 @@
       <c r="E15" s="8">
         <v>43122988</v>
       </c>
-      <c r="F15" s="14">
+      <c r="F15" s="12">
         <v>12</v>
       </c>
-      <c r="G15" s="12"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B16" s="6" t="s">
@@ -1778,12 +1758,11 @@
       <c r="E16" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="F16" s="14">
+      <c r="F16" s="12">
         <v>12</v>
       </c>
-      <c r="G16" s="12"/>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B17" s="6" t="s">
         <v>29</v>
       </c>
@@ -1796,12 +1775,11 @@
       <c r="E17" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="F17" s="14">
+      <c r="F17" s="12">
         <v>14.800000000000002</v>
       </c>
-      <c r="G17" s="12"/>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B18" s="6" t="s">
         <v>31</v>
       </c>
@@ -1814,12 +1792,11 @@
       <c r="E18" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F18" s="14">
+      <c r="F18" s="12">
         <v>6</v>
       </c>
-      <c r="G18" s="12"/>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B19" s="6" t="s">
         <v>33</v>
       </c>
@@ -1832,12 +1809,11 @@
       <c r="E19" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F19" s="14">
+      <c r="F19" s="12">
         <v>4</v>
       </c>
-      <c r="G19" s="12"/>
-    </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B20" s="6" t="s">
         <v>35</v>
       </c>
@@ -1850,12 +1826,11 @@
       <c r="E20" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="F20" s="14">
+      <c r="F20" s="12">
         <v>3</v>
       </c>
-      <c r="G20" s="12"/>
-    </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B21" s="6" t="s">
         <v>37</v>
       </c>
@@ -1868,12 +1843,11 @@
       <c r="E21" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="F21" s="14">
+      <c r="F21" s="12">
         <v>3</v>
       </c>
-      <c r="G21" s="12"/>
-    </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B22" s="6" t="s">
         <v>39</v>
       </c>
@@ -1886,12 +1860,11 @@
       <c r="E22" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="F22" s="14">
+      <c r="F22" s="12">
         <v>71</v>
       </c>
-      <c r="G22" s="12"/>
-    </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B23" s="6" t="s">
         <v>41</v>
       </c>
@@ -1904,12 +1877,11 @@
       <c r="E23" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F23" s="14">
+      <c r="F23" s="12">
         <v>189</v>
       </c>
-      <c r="G23" s="12"/>
-    </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B24" s="6" t="s">
         <v>43</v>
       </c>
@@ -1922,12 +1894,11 @@
       <c r="E24" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="F24" s="14">
+      <c r="F24" s="12">
         <v>64</v>
       </c>
-      <c r="G24" s="12"/>
-    </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B25" s="6" t="s">
         <v>45</v>
       </c>
@@ -1938,12 +1909,11 @@
       <c r="E25" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="F25" s="14">
+      <c r="F25" s="12">
         <v>0</v>
       </c>
-      <c r="G25" s="12"/>
-    </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B26" s="6" t="s">
         <v>47</v>
       </c>
@@ -1956,12 +1926,11 @@
       <c r="E26" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="F26" s="14">
+      <c r="F26" s="12">
         <v>-2</v>
       </c>
-      <c r="G26" s="12"/>
-    </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B27" s="6" t="s">
         <v>49</v>
       </c>
@@ -1972,12 +1941,11 @@
       <c r="E27" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="F27" s="14">
+      <c r="F27" s="12">
         <v>1</v>
       </c>
-      <c r="G27" s="12"/>
-    </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B28" s="6" t="s">
         <v>51</v>
       </c>
@@ -1990,12 +1958,11 @@
       <c r="E28" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="F28" s="14">
+      <c r="F28" s="12">
         <v>3</v>
       </c>
-      <c r="G28" s="12"/>
-    </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B29" s="6" t="s">
         <v>53</v>
       </c>
@@ -2008,12 +1975,11 @@
       <c r="E29" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="F29" s="14">
+      <c r="F29" s="12">
         <v>-1.0000000000000124</v>
       </c>
-      <c r="G29" s="12"/>
-    </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B30" s="6" t="s">
         <v>55</v>
       </c>
@@ -2026,12 +1992,11 @@
       <c r="E30" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="F30" s="14">
+      <c r="F30" s="12">
         <v>2.0000000000000133</v>
       </c>
-      <c r="G30" s="12"/>
-    </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B31" s="6" t="s">
         <v>57</v>
       </c>
@@ -2044,12 +2009,11 @@
       <c r="E31" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="F31" s="14">
+      <c r="F31" s="12">
         <v>-1.2434497875801753E-14</v>
       </c>
-      <c r="G31" s="12"/>
-    </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B32" s="6" t="s">
         <v>59</v>
       </c>
@@ -2062,12 +2026,11 @@
       <c r="E32" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="F32" s="14">
+      <c r="F32" s="12">
         <v>1.600000000000021</v>
       </c>
-      <c r="G32" s="12"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B33" s="6" t="s">
         <v>61</v>
       </c>
@@ -2080,12 +2043,11 @@
       <c r="E33" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="F33" s="14">
+      <c r="F33" s="12">
         <v>249</v>
       </c>
-      <c r="G33" s="12"/>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B34" s="6" t="s">
         <v>63</v>
       </c>
@@ -2098,12 +2060,11 @@
       <c r="E34" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="F34" s="14">
+      <c r="F34" s="12">
         <v>0</v>
       </c>
-      <c r="G34" s="12"/>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B35" s="6" t="s">
         <v>64</v>
       </c>
@@ -2114,12 +2075,11 @@
       <c r="E35" s="8">
         <v>43123024</v>
       </c>
-      <c r="F35" s="14">
+      <c r="F35" s="12">
         <v>0</v>
       </c>
-      <c r="G35" s="12"/>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
         <v>292</v>
       </c>
@@ -2135,12 +2095,11 @@
       <c r="E36" s="8">
         <v>43123030</v>
       </c>
-      <c r="F36" s="14">
+      <c r="F36" s="12">
         <v>91</v>
       </c>
-      <c r="G36" s="12"/>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
         <v>292</v>
       </c>
@@ -2156,12 +2115,11 @@
       <c r="E37" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="F37" s="14">
+      <c r="F37" s="12">
         <v>15</v>
       </c>
-      <c r="G37" s="12"/>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
         <v>292</v>
       </c>
@@ -2177,12 +2135,11 @@
       <c r="E38" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="F38" s="14">
+      <c r="F38" s="12">
         <v>39</v>
       </c>
-      <c r="G38" s="12"/>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
         <v>292</v>
       </c>
@@ -2198,12 +2155,11 @@
       <c r="E39" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="F39" s="14">
+      <c r="F39" s="12">
         <v>16</v>
       </c>
-      <c r="G39" s="12"/>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
         <v>292</v>
       </c>
@@ -2219,12 +2175,11 @@
       <c r="E40" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="F40" s="14">
+      <c r="F40" s="12">
         <v>8</v>
       </c>
-      <c r="G40" s="12"/>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
         <v>291</v>
       </c>
@@ -2240,12 +2195,11 @@
       <c r="E41" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="F41" s="14">
+      <c r="F41" s="12">
         <v>29</v>
       </c>
-      <c r="G41" s="12"/>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
         <v>291</v>
       </c>
@@ -2261,12 +2215,11 @@
       <c r="E42" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="F42" s="14">
+      <c r="F42" s="12">
         <v>0</v>
       </c>
-      <c r="G42" s="12"/>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
         <v>291</v>
       </c>
@@ -2282,12 +2235,11 @@
       <c r="E43" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="F43" s="14">
+      <c r="F43" s="12">
         <v>9</v>
       </c>
-      <c r="G43" s="12"/>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
         <v>291</v>
       </c>
@@ -2303,12 +2255,11 @@
       <c r="E44" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="F44" s="14">
+      <c r="F44" s="12">
         <v>38</v>
       </c>
-      <c r="G44" s="12"/>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
         <v>291</v>
       </c>
@@ -2324,12 +2275,11 @@
       <c r="E45" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="F45" s="14">
+      <c r="F45" s="12">
         <v>10</v>
       </c>
-      <c r="G45" s="12"/>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
         <v>296</v>
       </c>
@@ -2345,12 +2295,11 @@
       <c r="E46" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="F46" s="14">
+      <c r="F46" s="12">
         <v>-8</v>
       </c>
-      <c r="G46" s="12"/>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
         <v>296</v>
       </c>
@@ -2364,12 +2313,11 @@
       <c r="E47" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="F47" s="14">
+      <c r="F47" s="12">
         <v>35</v>
       </c>
-      <c r="G47" s="12"/>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
         <v>296</v>
       </c>
@@ -2385,12 +2333,11 @@
       <c r="E48" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="F48" s="14">
+      <c r="F48" s="12">
         <v>33</v>
       </c>
-      <c r="G48" s="12"/>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
         <v>293</v>
       </c>
@@ -2406,12 +2353,11 @@
       <c r="E49" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="F49" s="14">
+      <c r="F49" s="12">
         <v>19</v>
       </c>
-      <c r="G49" s="12"/>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
         <v>293</v>
       </c>
@@ -2427,12 +2373,11 @@
       <c r="E50" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="F50" s="14">
+      <c r="F50" s="12">
         <v>39</v>
       </c>
-      <c r="G50" s="12"/>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B51" s="6" t="s">
         <v>95</v>
       </c>
@@ -2443,12 +2388,11 @@
       <c r="E51" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="F51" s="14">
+      <c r="F51" s="12">
         <v>0</v>
       </c>
-      <c r="G51" s="12"/>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B52" s="6" t="s">
         <v>97</v>
       </c>
@@ -2459,12 +2403,11 @@
       <c r="E52" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="F52" s="14">
+      <c r="F52" s="12">
         <v>0</v>
       </c>
-      <c r="G52" s="12"/>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" s="5" t="s">
         <v>294</v>
       </c>
@@ -2480,12 +2423,11 @@
       <c r="E53" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="F53" s="14">
+      <c r="F53" s="12">
         <v>9</v>
       </c>
-      <c r="G53" s="12"/>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" s="5" t="s">
         <v>294</v>
       </c>
@@ -2501,12 +2443,11 @@
       <c r="E54" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="F54" s="14">
+      <c r="F54" s="12">
         <v>21</v>
       </c>
-      <c r="G54" s="12"/>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" s="5" t="s">
         <v>295</v>
       </c>
@@ -2522,12 +2463,11 @@
       <c r="E55" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="F55" s="14">
+      <c r="F55" s="12">
         <v>18</v>
       </c>
-      <c r="G55" s="12"/>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" s="5" t="s">
         <v>295</v>
       </c>
@@ -2543,12 +2483,11 @@
       <c r="E56" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="F56" s="14">
+      <c r="F56" s="12">
         <v>0</v>
       </c>
-      <c r="G56" s="12"/>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" s="5" t="s">
         <v>295</v>
       </c>
@@ -2564,12 +2503,11 @@
       <c r="E57" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="F57" s="14">
+      <c r="F57" s="12">
         <v>0</v>
       </c>
-      <c r="G57" s="12"/>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" s="5" t="s">
         <v>289</v>
       </c>
@@ -2583,12 +2521,11 @@
       <c r="E58" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="F58" s="14">
+      <c r="F58" s="12">
         <v>36</v>
       </c>
-      <c r="G58" s="12"/>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" s="5" t="s">
         <v>289</v>
       </c>
@@ -2602,12 +2539,11 @@
       <c r="E59" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="F59" s="14">
+      <c r="F59" s="12">
         <v>13</v>
       </c>
-      <c r="G59" s="12"/>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" s="5" t="s">
         <v>289</v>
       </c>
@@ -2621,12 +2557,11 @@
       <c r="E60" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="F60" s="14">
+      <c r="F60" s="12">
         <v>8</v>
       </c>
-      <c r="G60" s="12"/>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
         <v>286</v>
       </c>
@@ -2642,12 +2577,11 @@
       <c r="E61" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="F61" s="14">
+      <c r="F61" s="12">
         <v>-9</v>
       </c>
-      <c r="G61" s="12"/>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" s="5" t="s">
         <v>287</v>
       </c>
@@ -2663,12 +2597,11 @@
       <c r="E62" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="F62" s="14">
+      <c r="F62" s="12">
         <v>42</v>
       </c>
-      <c r="G62" s="12"/>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" s="5" t="s">
         <v>287</v>
       </c>
@@ -2684,12 +2617,11 @@
       <c r="E63" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="F63" s="14">
+      <c r="F63" s="12">
         <v>9</v>
       </c>
-      <c r="G63" s="12"/>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B64" s="6" t="s">
         <v>121</v>
       </c>
@@ -2702,12 +2634,11 @@
       <c r="E64" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="F64" s="14">
+      <c r="F64" s="12">
         <v>0</v>
       </c>
-      <c r="G64" s="12"/>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B65" s="6" t="s">
         <v>123</v>
       </c>
@@ -2720,12 +2651,11 @@
       <c r="E65" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="F65" s="14">
+      <c r="F65" s="12">
         <v>2</v>
       </c>
-      <c r="G65" s="12"/>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B66" s="6" t="s">
         <v>125</v>
       </c>
@@ -2738,12 +2668,11 @@
       <c r="E66" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="F66" s="14">
+      <c r="F66" s="12">
         <v>4</v>
       </c>
-      <c r="G66" s="12"/>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" s="5" t="s">
         <v>288</v>
       </c>
@@ -2754,17 +2683,16 @@
         <v>276</v>
       </c>
       <c r="D67" s="13">
-        <v>5.53</v>
+        <v>5.03</v>
       </c>
       <c r="E67" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="F67" s="14">
+      <c r="F67" s="12">
         <v>10</v>
       </c>
-      <c r="G67" s="12"/>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" s="5" t="s">
         <v>288</v>
       </c>
@@ -2780,12 +2708,11 @@
       <c r="E68" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="F68" s="14">
+      <c r="F68" s="12">
         <v>18</v>
       </c>
-      <c r="G68" s="12"/>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" s="5" t="s">
         <v>288</v>
       </c>
@@ -2801,12 +2728,11 @@
       <c r="E69" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="F69" s="14">
+      <c r="F69" s="12">
         <v>12</v>
       </c>
-      <c r="G69" s="12"/>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" s="5" t="s">
         <v>282</v>
       </c>
@@ -2822,12 +2748,11 @@
       <c r="E70" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="F70" s="14">
+      <c r="F70" s="12">
         <v>15</v>
       </c>
-      <c r="G70" s="12"/>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" s="5" t="s">
         <v>282</v>
       </c>
@@ -2843,12 +2768,11 @@
       <c r="E71" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="F71" s="14">
+      <c r="F71" s="12">
         <v>9</v>
       </c>
-      <c r="G71" s="12"/>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B72" s="6" t="s">
         <v>137</v>
       </c>
@@ -2856,17 +2780,16 @@
         <v>274</v>
       </c>
       <c r="D72" s="13">
-        <v>1.6500000000000001</v>
+        <v>0.71</v>
       </c>
       <c r="E72" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="F72" s="14">
+      <c r="F72" s="12">
         <v>0</v>
       </c>
-      <c r="G72" s="12"/>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B73" s="6" t="s">
         <v>139</v>
       </c>
@@ -2874,17 +2797,16 @@
         <v>274</v>
       </c>
       <c r="D73" s="13">
-        <v>1.6500000000000001</v>
+        <v>0.71</v>
       </c>
       <c r="E73" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="F73" s="14">
+      <c r="F73" s="12">
         <v>0</v>
       </c>
-      <c r="G73" s="12"/>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" s="5" t="s">
         <v>304</v>
       </c>
@@ -2900,12 +2822,11 @@
       <c r="E74" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="F74" s="14">
+      <c r="F74" s="12">
         <v>91</v>
       </c>
-      <c r="G74" s="12"/>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" s="5" t="s">
         <v>304</v>
       </c>
@@ -2921,12 +2842,11 @@
       <c r="E75" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="F75" s="14">
+      <c r="F75" s="12">
         <v>8</v>
       </c>
-      <c r="G75" s="12"/>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" s="5" t="s">
         <v>303</v>
       </c>
@@ -2942,12 +2862,11 @@
       <c r="E76" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="F76" s="14">
+      <c r="F76" s="12">
         <v>13</v>
       </c>
-      <c r="G76" s="12"/>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" s="5" t="s">
         <v>311</v>
       </c>
@@ -2963,12 +2882,11 @@
       <c r="E77" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="F77" s="14">
+      <c r="F77" s="12">
         <v>20</v>
       </c>
-      <c r="G77" s="12"/>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" s="5" t="s">
         <v>311</v>
       </c>
@@ -2984,12 +2902,11 @@
       <c r="E78" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="F78" s="14">
+      <c r="F78" s="12">
         <v>13</v>
       </c>
-      <c r="G78" s="12"/>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" s="5" t="s">
         <v>311</v>
       </c>
@@ -3005,12 +2922,11 @@
       <c r="E79" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="F79" s="14">
+      <c r="F79" s="12">
         <v>0</v>
       </c>
-      <c r="G79" s="12"/>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" s="5" t="s">
         <v>310</v>
       </c>
@@ -3026,12 +2942,11 @@
       <c r="E80" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="F80" s="14">
+      <c r="F80" s="12">
         <v>50</v>
       </c>
-      <c r="G80" s="12"/>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" s="5" t="s">
         <v>310</v>
       </c>
@@ -3047,12 +2962,11 @@
       <c r="E81" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="F81" s="14">
+      <c r="F81" s="12">
         <v>32</v>
       </c>
-      <c r="G81" s="12"/>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" s="5" t="s">
         <v>310</v>
       </c>
@@ -3068,12 +2982,11 @@
       <c r="E82" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="F82" s="14">
+      <c r="F82" s="12">
         <v>9</v>
       </c>
-      <c r="G82" s="12"/>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" s="5" t="s">
         <v>313</v>
       </c>
@@ -3089,12 +3002,11 @@
       <c r="E83" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="F83" s="14">
+      <c r="F83" s="12">
         <v>32</v>
       </c>
-      <c r="G83" s="12"/>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" s="5" t="s">
         <v>313</v>
       </c>
@@ -3110,12 +3022,11 @@
       <c r="E84" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="F84" s="14">
+      <c r="F84" s="12">
         <v>33</v>
       </c>
-      <c r="G84" s="12"/>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" s="5" t="s">
         <v>313</v>
       </c>
@@ -3131,12 +3042,11 @@
       <c r="E85" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="F85" s="14">
+      <c r="F85" s="12">
         <v>24</v>
       </c>
-      <c r="G85" s="12"/>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" s="5" t="s">
         <v>306</v>
       </c>
@@ -3152,12 +3062,11 @@
       <c r="E86" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="F86" s="14">
+      <c r="F86" s="12">
         <v>20</v>
       </c>
-      <c r="G86" s="12"/>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" s="5" t="s">
         <v>306</v>
       </c>
@@ -3173,12 +3082,11 @@
       <c r="E87" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="F87" s="14">
+      <c r="F87" s="12">
         <v>23</v>
       </c>
-      <c r="G87" s="12"/>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" s="5" t="s">
         <v>306</v>
       </c>
@@ -3194,12 +3102,11 @@
       <c r="E88" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="F88" s="14">
+      <c r="F88" s="12">
         <v>38</v>
       </c>
-      <c r="G88" s="12"/>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" s="5" t="s">
         <v>309</v>
       </c>
@@ -3215,12 +3122,11 @@
       <c r="E89" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="F89" s="14">
+      <c r="F89" s="12">
         <v>90</v>
       </c>
-      <c r="G89" s="12"/>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" s="5" t="s">
         <v>309</v>
       </c>
@@ -3236,12 +3142,11 @@
       <c r="E90" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="F90" s="14">
+      <c r="F90" s="12">
         <v>76</v>
       </c>
-      <c r="G90" s="12"/>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" s="5" t="s">
         <v>309</v>
       </c>
@@ -3257,12 +3162,11 @@
       <c r="E91" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="F91" s="14">
+      <c r="F91" s="12">
         <v>46</v>
       </c>
-      <c r="G91" s="12"/>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" s="5" t="s">
         <v>309</v>
       </c>
@@ -3273,17 +3177,16 @@
         <v>256</v>
       </c>
       <c r="D92" s="13">
-        <v>5.1100000000000003</v>
+        <v>2.61</v>
       </c>
       <c r="E92" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="F92" s="14">
+      <c r="F92" s="12">
         <v>47</v>
       </c>
-      <c r="G92" s="12"/>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" s="5" t="s">
         <v>309</v>
       </c>
@@ -3299,12 +3202,11 @@
       <c r="E93" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="F93" s="14">
+      <c r="F93" s="12">
         <v>6</v>
       </c>
-      <c r="G93" s="12"/>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" s="5" t="s">
         <v>307</v>
       </c>
@@ -3320,12 +3222,11 @@
       <c r="E94" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="F94" s="14">
+      <c r="F94" s="12">
         <v>2</v>
       </c>
-      <c r="G94" s="12"/>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" s="5" t="s">
         <v>307</v>
       </c>
@@ -3341,12 +3242,11 @@
       <c r="E95" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="F95" s="14">
+      <c r="F95" s="12">
         <v>75</v>
       </c>
-      <c r="G95" s="12"/>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" s="5" t="s">
         <v>307</v>
       </c>
@@ -3362,12 +3262,11 @@
       <c r="E96" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="F96" s="14">
+      <c r="F96" s="12">
         <v>83</v>
       </c>
-      <c r="G96" s="12"/>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" s="5" t="s">
         <v>307</v>
       </c>
@@ -3378,17 +3277,16 @@
         <v>254</v>
       </c>
       <c r="D97" s="13">
-        <v>7.84</v>
+        <v>13.99</v>
       </c>
       <c r="E97" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="F97" s="14">
+      <c r="F97" s="12">
         <v>49</v>
       </c>
-      <c r="G97" s="12"/>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" s="5" t="s">
         <v>307</v>
       </c>
@@ -3404,12 +3302,11 @@
       <c r="E98" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="F98" s="14">
+      <c r="F98" s="12">
         <v>0</v>
       </c>
-      <c r="G98" s="12"/>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" s="5" t="s">
         <v>300</v>
       </c>
@@ -3425,12 +3322,11 @@
       <c r="E99" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="F99" s="14">
+      <c r="F99" s="12">
         <v>79</v>
       </c>
-      <c r="G99" s="12"/>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" s="5" t="s">
         <v>300</v>
       </c>
@@ -3441,17 +3337,16 @@
         <v>254</v>
       </c>
       <c r="D100" s="13">
-        <v>6.87</v>
+        <v>7.28</v>
       </c>
       <c r="E100" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="F100" s="14">
+      <c r="F100" s="12">
         <v>35</v>
       </c>
-      <c r="G100" s="12"/>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" s="5" t="s">
         <v>300</v>
       </c>
@@ -3467,12 +3362,11 @@
       <c r="E101" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="F101" s="14">
+      <c r="F101" s="12">
         <v>0</v>
       </c>
-      <c r="G101" s="12"/>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" s="5" t="s">
         <v>299</v>
       </c>
@@ -3488,12 +3382,11 @@
       <c r="E102" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="F102" s="14">
+      <c r="F102" s="12">
         <v>106</v>
       </c>
-      <c r="G102" s="12"/>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" s="5" t="s">
         <v>299</v>
       </c>
@@ -3509,12 +3402,11 @@
       <c r="E103" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="F103" s="14">
+      <c r="F103" s="12">
         <v>31</v>
       </c>
-      <c r="G103" s="12"/>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" s="5" t="s">
         <v>299</v>
       </c>
@@ -3530,12 +3422,11 @@
       <c r="E104" s="8" t="s">
         <v>200</v>
       </c>
-      <c r="F104" s="14">
+      <c r="F104" s="12">
         <v>29</v>
       </c>
-      <c r="G104" s="12"/>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" s="5" t="s">
         <v>302</v>
       </c>
@@ -3551,12 +3442,11 @@
       <c r="E105" s="8" t="s">
         <v>202</v>
       </c>
-      <c r="F105" s="14">
+      <c r="F105" s="12">
         <v>51</v>
       </c>
-      <c r="G105" s="12"/>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" s="5" t="s">
         <v>302</v>
       </c>
@@ -3572,12 +3462,11 @@
       <c r="E106" s="8" t="s">
         <v>204</v>
       </c>
-      <c r="F106" s="14">
+      <c r="F106" s="12">
         <v>21</v>
       </c>
-      <c r="G106" s="12"/>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" s="5" t="s">
         <v>302</v>
       </c>
@@ -3593,12 +3482,11 @@
       <c r="E107" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="F107" s="14">
+      <c r="F107" s="12">
         <v>3</v>
       </c>
-      <c r="G107" s="12"/>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" s="5" t="s">
         <v>302</v>
       </c>
@@ -3614,12 +3502,11 @@
       <c r="E108" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="F108" s="14">
+      <c r="F108" s="12">
         <v>0</v>
       </c>
-      <c r="G108" s="12"/>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" s="5" t="s">
         <v>301</v>
       </c>
@@ -3635,12 +3522,11 @@
       <c r="E109" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="F109" s="14">
+      <c r="F109" s="12">
         <v>88</v>
       </c>
-      <c r="G109" s="12"/>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110" s="5" t="s">
         <v>301</v>
       </c>
@@ -3656,12 +3542,11 @@
       <c r="E110" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="F110" s="14">
+      <c r="F110" s="12">
         <v>66</v>
       </c>
-      <c r="G110" s="12"/>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" s="5" t="s">
         <v>301</v>
       </c>
@@ -3677,12 +3562,11 @@
       <c r="E111" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="F111" s="14">
+      <c r="F111" s="12">
         <v>0</v>
       </c>
-      <c r="G111" s="12"/>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112" s="5" t="s">
         <v>301</v>
       </c>
@@ -3698,12 +3582,11 @@
       <c r="E112" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="F112" s="14">
+      <c r="F112" s="12">
         <v>26</v>
       </c>
-      <c r="G112" s="12"/>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A113" s="5" t="s">
         <v>298</v>
       </c>
@@ -3719,12 +3602,11 @@
       <c r="E113" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="F113" s="14">
+      <c r="F113" s="12">
         <v>3</v>
       </c>
-      <c r="G113" s="12"/>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A114" s="5" t="s">
         <v>298</v>
       </c>
@@ -3740,12 +3622,11 @@
       <c r="E114" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="F114" s="14">
+      <c r="F114" s="12">
         <v>8</v>
       </c>
-      <c r="G114" s="12"/>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B115" s="6" t="s">
         <v>223</v>
       </c>
@@ -3758,12 +3639,11 @@
       <c r="E115" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="F115" s="14">
+      <c r="F115" s="12">
         <v>20</v>
       </c>
-      <c r="G115" s="12"/>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B116" s="6" t="s">
         <v>95</v>
       </c>
@@ -3774,12 +3654,11 @@
       <c r="E116" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="F116" s="14">
+      <c r="F116" s="12">
         <v>0</v>
       </c>
-      <c r="G116" s="12"/>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B117" s="6" t="s">
         <v>226</v>
       </c>
@@ -3792,12 +3671,11 @@
       <c r="E117" s="8" t="s">
         <v>225</v>
       </c>
-      <c r="F117" s="14">
+      <c r="F117" s="12">
         <v>11</v>
       </c>
-      <c r="G117" s="12"/>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B118" s="6" t="s">
         <v>228</v>
       </c>
@@ -3810,12 +3688,11 @@
       <c r="E118" s="8" t="s">
         <v>227</v>
       </c>
-      <c r="F118" s="14">
+      <c r="F118" s="12">
         <v>12</v>
       </c>
-      <c r="G118" s="12"/>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B119" s="6" t="s">
         <v>230</v>
       </c>
@@ -3828,12 +3705,11 @@
       <c r="E119" s="8" t="s">
         <v>229</v>
       </c>
-      <c r="F119" s="14">
+      <c r="F119" s="12">
         <v>2</v>
       </c>
-      <c r="G119" s="12"/>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A120" s="5" t="s">
         <v>308</v>
       </c>
@@ -3849,12 +3725,11 @@
       <c r="E120" s="8" t="s">
         <v>231</v>
       </c>
-      <c r="F120" s="14">
+      <c r="F120" s="12">
         <v>32</v>
       </c>
-      <c r="G120" s="12"/>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A121" s="5" t="s">
         <v>308</v>
       </c>
@@ -3870,12 +3745,11 @@
       <c r="E121" s="8" t="s">
         <v>233</v>
       </c>
-      <c r="F121" s="14">
+      <c r="F121" s="12">
         <v>8</v>
       </c>
-      <c r="G121" s="12"/>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A122" s="5" t="s">
         <v>308</v>
       </c>
@@ -3891,12 +3765,11 @@
       <c r="E122" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="F122" s="14">
+      <c r="F122" s="12">
         <v>67</v>
       </c>
-      <c r="G122" s="12"/>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A123" s="5" t="s">
         <v>308</v>
       </c>
@@ -3912,12 +3785,11 @@
       <c r="E123" s="8" t="s">
         <v>237</v>
       </c>
-      <c r="F123" s="14">
+      <c r="F123" s="12">
         <v>24</v>
       </c>
-      <c r="G123" s="12"/>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A124" s="5" t="s">
         <v>308</v>
       </c>
@@ -3933,12 +3805,11 @@
       <c r="E124" s="8" t="s">
         <v>239</v>
       </c>
-      <c r="F124" s="14">
+      <c r="F124" s="12">
         <v>23</v>
       </c>
-      <c r="G124" s="12"/>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A125" s="5" t="s">
         <v>312</v>
       </c>
@@ -3954,12 +3825,11 @@
       <c r="E125" s="8" t="s">
         <v>241</v>
       </c>
-      <c r="F125" s="14">
+      <c r="F125" s="12">
         <v>130</v>
       </c>
-      <c r="G125" s="12"/>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A126" s="5" t="s">
         <v>312</v>
       </c>
@@ -3975,12 +3845,11 @@
       <c r="E126" s="8" t="s">
         <v>243</v>
       </c>
-      <c r="F126" s="14">
+      <c r="F126" s="12">
         <v>51</v>
       </c>
-      <c r="G126" s="12"/>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A127" s="5" t="s">
         <v>312</v>
       </c>
@@ -3996,12 +3865,11 @@
       <c r="E127" s="8">
         <v>43123133</v>
       </c>
-      <c r="F127" s="14">
+      <c r="F127" s="12">
         <v>27</v>
       </c>
-      <c r="G127" s="12"/>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A128" s="5" t="s">
         <v>297</v>
       </c>
@@ -4012,13 +3880,13 @@
         <v>253</v>
       </c>
       <c r="D128" s="7">
-        <v>7.67</v>
+        <v>7.74</v>
       </c>
       <c r="E128" s="9">
         <v>43107593</v>
       </c>
-      <c r="F128" s="11" t="s">
-        <v>315</v>
+      <c r="F128" s="11">
+        <v>18</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
@@ -4032,13 +3900,13 @@
         <v>253</v>
       </c>
       <c r="D129" s="7">
-        <v>7.67</v>
+        <v>7.74</v>
       </c>
       <c r="E129" s="9">
         <v>43107594</v>
       </c>
       <c r="F129" s="11">
-        <v>4</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
